--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/metropolitana.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/metropolitana.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M204"/>
+  <dimension ref="A1:M205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9452,7 +9452,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>14-189-CM26</t>
+          <t>14-190-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9507,13 +9507,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>3497.17</v>
+        <v>2797.74</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>14-190-CM26</t>
+          <t>14-189-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9568,7 +9568,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>2797.74</v>
+        <v>3497.17</v>
       </c>
     </row>
     <row r="150">
@@ -12827,7 +12827,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>585-94-CM26</t>
+          <t>514862-462-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12852,12 +12852,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>71.234.100-9</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>CORPORACION MUNICIPAL DE PENALOLEN PARA EL DESARRO</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -12867,12 +12867,12 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -12886,13 +12886,13 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>326243.38</v>
+        <v>21360.5</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>514862-462-CM26</t>
+          <t>585-94-CM26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12917,12 +12917,12 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>71.234.100-9</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE PENALOLEN PARA EL DESARRO</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -12932,12 +12932,12 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -12951,7 +12951,68 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>21360.5</v>
+        <v>326243.38</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>1375746-102-CM26</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>61.981.280-8</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ACONCAGUA</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Netsus SpA</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>76.288.338-4</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M205" s="2" t="n">
+        <v>16260.16</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/metropolitana.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/metropolitana.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M405"/>
+  <dimension ref="A1:M407"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2062,7 +2062,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4388-49-CM25</t>
+          <t>3323-21-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2087,12 +2087,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>60.511.000-2</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL INTERIOR</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2121,13 +2121,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>15440.27</v>
+        <v>888.7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3323-21-CM25</t>
+          <t>4388-49-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>60.511.000-2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SUBSECRETARIA DEL INTERIOR</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2186,7 +2186,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>888.7</v>
+        <v>15440.27</v>
       </c>
     </row>
     <row r="28">
@@ -2842,7 +2842,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4499-56-CM25</t>
+          <t>606-153-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.073.100-2</t>
+          <t>60.513.000-3</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO</t>
+          <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2882,12 +2882,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>ORION 2000 SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.899.890-0</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2901,13 +2901,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>14164.33</v>
+        <v>61145.18</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>606-153-CM25</t>
+          <t>4499-56-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2932,12 +2932,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>60.513.000-3</t>
+          <t>69.073.100-2</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2947,12 +2947,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>ORION 2000 SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>96.899.890-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>61145.18</v>
+        <v>14164.33</v>
       </c>
     </row>
     <row r="40">
@@ -3098,7 +3098,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2403-299-CM25</t>
+          <t>188-312-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3123,12 +3123,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.254.000-k</t>
+          <t>70.933.700-9</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENALOLEN</t>
+          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3157,13 +3157,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1174.58</v>
+        <v>16429.35</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>188-312-CM25</t>
+          <t>2403-299-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>70.933.700-9</t>
+          <t>69.254.000-k</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
+          <t>I MUNICIPALIDAD DE PENALOLEN</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3222,13 +3222,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>16429.35</v>
+        <v>1174.58</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1300-226-CM25</t>
+          <t>1736-2942-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3248,17 +3248,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.961.000-8</t>
+          <t>69.255.300-4</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL ADULTO MAYOR</t>
+          <t>I MUNICIPALIDAD DE LA COMUNA DE EL BOSQUE</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3268,12 +3268,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>GTD TELEDUCTOS S.A</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>880443249</t>
+          <t>88.983.600-8</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3283,13 +3283,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>59336.26</v>
+        <v>757.61</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1736-2942-CM25</t>
+          <t>1300-226-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3309,17 +3309,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.255.300-4</t>
+          <t>61.961.000-8</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA COMUNA DE EL BOSQUE</t>
+          <t>SERVICIO NACIONAL DEL ADULTO MAYOR</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>GTD TELEDUCTOS S.A</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>88.983.600-8</t>
+          <t>880443249</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3344,7 +3344,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>757.61</v>
+        <v>59336.26</v>
       </c>
     </row>
     <row r="46">
@@ -4130,7 +4130,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1057495-2941-CM25</t>
+          <t>699360-55-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.608.104-7</t>
+          <t>60.505.000-k</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD SUR HOSPITAL LUCIO CORDOVA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>LIVISTER CHILE SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>77.622.841-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4189,13 +4189,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>14178.85</v>
+        <v>8037.4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>699360-55-CM25</t>
+          <t>1057495-2941-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>60.505.000-k</t>
+          <t>61.608.104-7</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD SUR HOSPITAL LUCIO CORDOVA</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>LIVISTER CHILE SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>77.622.841-9</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4254,7 +4254,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>8037.4</v>
+        <v>14178.85</v>
       </c>
     </row>
     <row r="60">
@@ -4455,7 +4455,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1057499-258-CM25</t>
+          <t>1057473-261-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.608.108-K</t>
+          <t>61.999.030-7</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
+          <t>Centro Metropolitano de Atención Prehospitalaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4495,28 +4495,32 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>151139.52</v>
+        <v>70821.66</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1057473-261-CM25</t>
+          <t>798018-37-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4541,12 +4545,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.999.030-7</t>
+          <t>65.073.222-7</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Centro Metropolitano de Atención Prehospitalaria</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4556,12 +4560,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4575,13 +4579,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>70821.66</v>
+        <v>4356.66</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>798018-37-CM25</t>
+          <t>1057499-258-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4606,12 +4610,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>65.073.222-7</t>
+          <t>61.608.108-K</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4621,26 +4625,22 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>4356.66</v>
+        <v>151139.52</v>
       </c>
     </row>
     <row r="66">
@@ -5093,7 +5093,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2770-168-CM25</t>
+          <t>2767-59-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>69.070.900-7</t>
+          <t>69.072.000-0</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAIPU</t>
+          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5133,28 +5133,32 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>407446.96</v>
+        <v>70821.66</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2767-59-CM25</t>
+          <t>2770-168-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5179,12 +5183,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>69.072.000-0</t>
+          <t>69.070.900-7</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
+          <t>I MUNICIPALIDAD DE MAIPU</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5194,26 +5198,22 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>70821.66</v>
+        <v>407446.96</v>
       </c>
     </row>
     <row r="75">
@@ -5284,7 +5284,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>711841-374-CM25</t>
+          <t>5684-339-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5304,17 +5304,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>60.103.000-4</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>ORION 2000 SPA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
+          <t>96.899.890-0</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5343,13 +5343,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>9127.42</v>
+        <v>2608.86</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>5684-339-CM25</t>
+          <t>711841-374-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5369,17 +5369,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.103.000-4</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5389,12 +5389,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>ORION 2000 SPA</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>96.899.890-0</t>
+          <t>76.083.145-k</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5408,7 +5408,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>2608.86</v>
+        <v>9127.42</v>
       </c>
     </row>
     <row r="78">
@@ -5865,7 +5865,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>14-363-CM25</t>
+          <t>2565-356-CM25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5890,12 +5890,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>69.090.700-3</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>I MUNICIPALIDAD DE CHEPICA</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5905,28 +5905,32 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>ORION 2000 SPA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
+          <t>96.899.890-0</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>27988.8</v>
+        <v>9882.299999999999</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2565-356-CM25</t>
+          <t>14-363-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5951,12 +5955,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>69.090.700-3</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHEPICA</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5966,26 +5970,22 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>ORION 2000 SPA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>96.899.890-0</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>9882.299999999999</v>
+        <v>27988.8</v>
       </c>
     </row>
     <row r="87">
@@ -6576,7 +6576,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>3328-2174-CM25</t>
+          <t>1051173-52-CM25</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6601,12 +6601,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>60.100.003-2</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>MINISTERIO SECRETARIA GENERAL DE LA PRESIDENCIA DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6616,32 +6616,28 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>8460.42</v>
+        <v>74403.8</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1051173-52-CM25</t>
+          <t>3328-2174-CM25</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6666,12 +6662,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>60.100.003-2</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>MINISTERIO SECRETARIA GENERAL DE LA PRESIDENCIA DE LA REPUBLICA</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6681,28 +6677,32 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>74403.8</v>
+        <v>8460.42</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1447790-6-CM25</t>
+          <t>188-662-CM25</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6722,17 +6722,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.608.500-k</t>
+          <t>70.933.700-9</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR ORIENTE</t>
+          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6742,32 +6742,28 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>ORION 2000 SPA</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>96.899.890-0</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.854.651-7</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>9131.01</v>
+        <v>34153</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1447792-9-CM25</t>
+          <t>1447790-6-CM25</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6826,13 +6822,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>13696.52</v>
+        <v>9131.01</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>188-662-CM25</t>
+          <t>1447792-9-CM25</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6852,17 +6848,17 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>70.933.700-9</t>
+          <t>61.608.500-k</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR ORIENTE</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6872,22 +6868,26 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>ORION 2000 SPA</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
+          <t>96.899.890-0</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>34153</v>
+        <v>13696.52</v>
       </c>
     </row>
     <row r="101">
@@ -7279,7 +7279,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2765-399-CM25</t>
+          <t>1602-101-CM25</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7299,17 +7299,17 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>69.072.000-0</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7319,12 +7319,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -7338,13 +7338,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>1544.62</v>
+        <v>31726.59</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1602-101-CM25</t>
+          <t>2765-399-CM25</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7364,17 +7364,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>69.072.000-0</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7384,12 +7384,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -7403,7 +7403,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>31726.59</v>
+        <v>1544.62</v>
       </c>
     </row>
     <row r="109">
@@ -7799,7 +7799,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1271178-278-CM25</t>
+          <t>2378-90-CM25</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7824,12 +7824,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>71.369.900-4</t>
+          <t>69.070.700-4</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL DE MACUL</t>
+          <t>I MUNICIPALIDAD DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7839,17 +7839,17 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7858,13 +7858,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>3172.66</v>
+        <v>68311.71000000001</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2378-90-CM25</t>
+          <t>1271178-278-CM25</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7889,12 +7889,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>69.070.700-4</t>
+          <t>71.369.900-4</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA FLORIDA</t>
+          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL DE MACUL</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7904,17 +7904,17 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7923,7 +7923,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>68311.71000000001</v>
+        <v>3172.66</v>
       </c>
     </row>
     <row r="117">
@@ -10237,7 +10237,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1019-548-CM25</t>
+          <t>608897-11250-CM25</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -10262,12 +10262,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.979.930-5</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -10296,13 +10296,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>4863.77</v>
+        <v>9727.92</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1019-549-CM25</t>
+          <t>1019-548-CM25</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -10342,28 +10342,32 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>73666.52</v>
+        <v>4863.77</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>608897-11250-CM25</t>
+          <t>1019-549-CM25</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -10388,12 +10392,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>61.979.930-5</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -10403,26 +10407,22 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>9727.92</v>
+        <v>73666.52</v>
       </c>
     </row>
     <row r="156">
@@ -10684,7 +10684,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1057500-626-CM25</t>
+          <t>1020-454-CM25</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10704,17 +10704,17 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>61.608.500-K</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR ORIENTE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10724,28 +10724,32 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>67173.12</v>
+        <v>245698.11</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1450519-14-CM25</t>
+          <t>1057500-626-CM25</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10765,17 +10769,17 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>61.999.390-K</t>
+          <t>61.608.500-K</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SEGURIDAD PUBLICA</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR ORIENTE</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10785,32 +10789,28 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
-        </is>
-      </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>5787.03</v>
+        <v>67173.12</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1020-454-CM25</t>
+          <t>1450519-14-CM25</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10835,12 +10835,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.999.390-K</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SUBSECRETARIA DE SEGURIDAD PUBLICA</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.334.381-2</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -10869,7 +10869,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>245698.11</v>
+        <v>5787.03</v>
       </c>
     </row>
     <row r="163">
@@ -11200,7 +11200,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1425525-63-CM25</t>
+          <t>761-720-CM25</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>62.000.560-6</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>AGENCIA NACIONAL DE CIBERSEGURIDAD</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -11259,7 +11259,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>13176.28</v>
+        <v>2641.8</v>
       </c>
     </row>
     <row r="169">
@@ -11326,7 +11326,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>761-720-CM25</t>
+          <t>1425525-63-CM25</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11351,12 +11351,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>60.515.000-4</t>
+          <t>62.000.560-6</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
+          <t>AGENCIA NACIONAL DE CIBERSEGURIDAD</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -11366,12 +11366,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -11385,7 +11385,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>2641.8</v>
+        <v>13176.28</v>
       </c>
     </row>
     <row r="171">
@@ -11708,7 +11708,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>872-615-CM25</t>
+          <t>761-719-CM25</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11728,17 +11728,17 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>82.983.100-7</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Comisión Chilena de Energía Nuclear</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11748,17 +11748,17 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>XERTICA CHILE SPA</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.223.453-8</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -11767,13 +11767,13 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>2326.09</v>
+        <v>100143.74</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>761-719-CM25</t>
+          <t>514862-1032-CM25</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11793,17 +11793,17 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>60.515.000-4</t>
+          <t>71.234.100-9</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
+          <t>CORPORACION MUNICIPAL DE PENALOLEN PARA EL DESARROLO SOCIAL CORMUP</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>XERTICA CHILE SPA</t>
+          <t>SEIDOR TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>77.223.453-8</t>
+          <t>76.449.580-2</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -11832,13 +11832,13 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>100143.74</v>
+        <v>129944.43</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>514862-1032-CM25</t>
+          <t>872-615-CM25</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11863,12 +11863,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>71.234.100-9</t>
+          <t>82.983.100-7</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE PENALOLEN PARA EL DESARROLO SOCIAL CORMUP</t>
+          <t>Comisión Chilena de Energía Nuclear</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11878,17 +11878,17 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>SEIDOR TECHNOLOGIES S.A.</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>76.449.580-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -11897,7 +11897,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>129944.43</v>
+        <v>2326.09</v>
       </c>
     </row>
     <row r="179">
@@ -12163,7 +12163,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>857-221-CM25</t>
+          <t>577290-220-CM25</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -12188,12 +12188,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>72.576.700-5</t>
+          <t>61.979.750-7</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE LA DISCAPACIDAD</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -12222,13 +12222,13 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>19796.96</v>
+        <v>25374.13</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>577290-220-CM25</t>
+          <t>857-221-CM25</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>61.979.750-7</t>
+          <t>72.576.700-5</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TRANSPORTES</t>
+          <t>SERVICIO NACIONAL DE LA DISCAPACIDAD</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -12287,7 +12287,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>25374.13</v>
+        <v>19796.96</v>
       </c>
     </row>
     <row r="185">
@@ -12878,7 +12878,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>628-440-CM25</t>
+          <t>628-490-CM25</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12918,12 +12918,12 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>XERTICA CHILE SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>77.223.453-8</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -12937,13 +12937,13 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>94180.98</v>
+        <v>6678.28</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>628-483-CM25</t>
+          <t>870-391-CM25</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12968,12 +12968,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>60.107.000-6</t>
+          <t>60.718.000-8</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
+          <t>COMISION NACIONAL DE RIEGO</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -13002,13 +13002,13 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>21145.11</v>
+        <v>3078.29</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>870-391-CM25</t>
+          <t>628-440-CM25</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -13033,12 +13033,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>60.718.000-8</t>
+          <t>60.107.000-6</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>COMISION NACIONAL DE RIEGO</t>
+          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -13048,12 +13048,12 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>XERTICA CHILE SPA</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.223.453-8</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -13067,13 +13067,13 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>3078.29</v>
+        <v>94180.98</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>628-490-CM25</t>
+          <t>628-483-CM25</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -13132,7 +13132,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>6678.28</v>
+        <v>21145.11</v>
       </c>
     </row>
     <row r="198">
@@ -13398,7 +13398,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>605-503-CM25</t>
+          <t>2674-1249-CM25</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -13423,12 +13423,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>61.006.000-5</t>
+          <t>69.072.900-8</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Consejo de Defensa del Estado</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -13438,12 +13438,12 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -13457,13 +13457,13 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>16779</v>
+        <v>3171.77</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2674-1249-CM25</t>
+          <t>605-503-CM25</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -13488,12 +13488,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>69.072.900-8</t>
+          <t>61.006.000-5</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
+          <t>Consejo de Defensa del Estado</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -13503,12 +13503,12 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -13522,7 +13522,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>3171.77</v>
+        <v>16779</v>
       </c>
     </row>
     <row r="204">
@@ -13593,7 +13593,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1075952-49-CM25</t>
+          <t>918434-545-CM25</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -13618,12 +13618,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>62.000.580-0</t>
+          <t>61.980.680-8</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Superintendencia de Educación Superior</t>
+          <t>MINISTERIO DE LA MUJER Y LA EQUIDAD DE GÉNERO</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -13652,13 +13652,13 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>800.87</v>
+        <v>5503.32</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>918434-545-CM25</t>
+          <t>1075952-49-CM25</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13683,12 +13683,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>61.980.680-8</t>
+          <t>62.000.580-0</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>MINISTERIO DE LA MUJER Y LA EQUIDAD DE GÉNERO</t>
+          <t>Superintendencia de Educación Superior</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13717,7 +13717,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>5503.32</v>
+        <v>800.87</v>
       </c>
     </row>
     <row r="207">
@@ -16311,7 +16311,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1372962-3-CM26</t>
+          <t>1415862-13-CM26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -16331,17 +16331,17 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>65.143.474-2</t>
+          <t>61.533.000-0</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>FUNDACION PARA LA REHABILITACIÓN DE PERSONAS CON DISCAPACIDAD DE LA COMUNA DE SAN PEDRO DE ATACAMA</t>
+          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -16370,13 +16370,13 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>1651.17</v>
+        <v>70962.08</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1415862-13-CM26</t>
+          <t>1372962-3-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -16396,17 +16396,17 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>61.533.000-0</t>
+          <t>65.143.474-2</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
+          <t>FUNDACION PARA LA REHABILITACIÓN DE PERSONAS CON DISCAPACIDAD DE LA COMUNA DE SAN PEDRO DE ATACAMA</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -16435,7 +16435,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>70962.08</v>
+        <v>1651.17</v>
       </c>
     </row>
     <row r="249">
@@ -17083,7 +17083,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>1386073-60-CM26</t>
+          <t>1388961-131-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -17103,17 +17103,17 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>71.004.200-4</t>
+          <t>65.118.035-K</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>CORP CULTURAL DE LAS CONDES</t>
+          <t>ASOCIACION DE MUNICIPALIDADES PARA LA SEGURIDAD CIUDADANA EN LA ZONA ORIENTE</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -17123,32 +17123,28 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>SUPER SOFTWARE SPA</t>
+          <t>ASESORIAS EN INFORMATICA ZONA-TI LIMITADA</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>76.486.150-7</t>
-        </is>
-      </c>
-      <c r="K259" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.338.883-2</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr"/>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>15244.28</v>
+        <v>6417.17</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>1388961-131-CM26</t>
+          <t>1386073-60-CM26</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -17168,17 +17164,17 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>65.118.035-K</t>
+          <t>71.004.200-4</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>ASOCIACION DE MUNICIPALIDADES PARA LA SEGURIDAD CIUDADANA EN LA ZONA ORIENTE</t>
+          <t>CORP CULTURAL DE LAS CONDES</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -17188,28 +17184,32 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>ASESORIAS EN INFORMATICA ZONA-TI LIMITADA</t>
+          <t>SUPER SOFTWARE SPA</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>76.338.883-2</t>
-        </is>
-      </c>
-      <c r="K260" t="inlineStr"/>
+          <t>76.486.150-7</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>6417.17</v>
+        <v>15244.28</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>4928-21-CM26</t>
+          <t>1075952-14-CM26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -17234,12 +17234,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>62.000.580-0</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>Superintendencia de Educación Superior</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -17249,12 +17249,12 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.334.381-2</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
@@ -17268,13 +17268,13 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>11412.58</v>
+        <v>47829.67</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>1075952-14-CM26</t>
+          <t>4928-21-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -17299,12 +17299,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>62.000.580-0</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Superintendencia de Educación Superior</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -17314,12 +17314,12 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
@@ -17333,7 +17333,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>47829.67</v>
+        <v>11412.58</v>
       </c>
     </row>
     <row r="263">
@@ -17851,7 +17851,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>1216088-95-CM26</t>
+          <t>4294-60-CM26</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -17876,12 +17876,12 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>65.065.121-9</t>
+          <t>65.077.010-2</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES DE PUENTE ALTO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -17891,17 +17891,17 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -17910,13 +17910,13 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>845.38</v>
+        <v>14794.08</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>4294-60-CM26</t>
+          <t>1216088-95-CM26</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -17941,12 +17941,12 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>65.077.010-2</t>
+          <t>65.065.121-9</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES DE PUENTE ALTO</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -17956,17 +17956,17 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -17975,7 +17975,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>14794.08</v>
+        <v>845.38</v>
       </c>
     </row>
     <row r="273">
@@ -18371,7 +18371,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>610-21-CM26</t>
+          <t>2580-175-CM26</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -18396,12 +18396,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>61.707.000-6</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Comisión Nacional de Energía</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -18411,32 +18411,28 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K279" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.854.651-7</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>2941.38</v>
+        <v>15856.75</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2580-175-CM26</t>
+          <t>610-21-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -18461,12 +18457,12 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>61.707.000-6</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>Comisión Nacional de Energía</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -18476,28 +18472,32 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
-        </is>
-      </c>
-      <c r="K280" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>15856.75</v>
+        <v>2941.38</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2343-162-CM26</t>
+          <t>699360-19-CM26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -18522,12 +18522,12 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>69.070.100-6</t>
+          <t>60.505.000-k</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTIAGO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -18537,17 +18537,17 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
@@ -18556,13 +18556,13 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>2536.13</v>
+        <v>4325.59</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>1428670-72-CM26</t>
+          <t>2343-162-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -18582,17 +18582,17 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>65.117.794-4</t>
+          <t>69.070.100-6</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>ASOCIACION METROPOLITANA DE MUNICIPALIDADES DE SANTIAGO SUR PARA LA GE</t>
+          <t>I MUNICIPALIDAD DE SANTIAGO</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -18602,28 +18602,32 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>79.770.640-k</t>
-        </is>
-      </c>
-      <c r="K282" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>9507.48</v>
+        <v>2536.13</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>699360-19-CM26</t>
+          <t>1428670-72-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -18643,17 +18647,17 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>60.505.000-k</t>
+          <t>65.117.794-4</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>ASOCIACION METROPOLITANA DE MUNICIPALIDADES DE SANTIAGO SUR PARA LA GE</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -18663,26 +18667,22 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K283" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.770.640-k</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr"/>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>4325.59</v>
+        <v>9507.48</v>
       </c>
     </row>
     <row r="284">
@@ -18753,7 +18753,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>4928-38-CM26</t>
+          <t>5684-256-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -18778,12 +18778,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -18793,12 +18793,12 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
@@ -18812,13 +18812,13 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>4617.6</v>
+        <v>2461.68</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>5684-256-CM26</t>
+          <t>4928-38-CM26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -18843,12 +18843,12 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -18858,12 +18858,12 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
@@ -18877,7 +18877,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>2461.68</v>
+        <v>4617.6</v>
       </c>
     </row>
     <row r="287">
@@ -19269,7 +19269,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2069-4322-CM26</t>
+          <t>577290-48-CM26</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -19294,12 +19294,12 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.979.750-7</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -19309,12 +19309,12 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
@@ -19328,13 +19328,13 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>1031.66</v>
+        <v>4226.88</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>577290-48-CM26</t>
+          <t>2069-4322-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -19359,12 +19359,12 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>61.979.750-7</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TRANSPORTES</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -19374,12 +19374,12 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
@@ -19393,7 +19393,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>4226.88</v>
+        <v>1031.66</v>
       </c>
     </row>
     <row r="295">
@@ -19529,7 +19529,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>577290-45-CM26</t>
+          <t>14-185-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>61.979.750-7</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TRANSPORTES</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -19569,28 +19569,32 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>79.770.640-k</t>
-        </is>
-      </c>
-      <c r="K297" t="inlineStr"/>
+          <t>76.083.145-k</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>2579.33</v>
+        <v>3846.89</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>14-185-CM26</t>
+          <t>14-189-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -19649,13 +19653,13 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>3846.89</v>
+        <v>3497.17</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>14-186-CM26</t>
+          <t>14-190-CM26</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -19714,13 +19718,13 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>17602.43</v>
+        <v>2797.74</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>14-187-CM26</t>
+          <t>14-188-CM26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -19779,13 +19783,13 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>17485.86</v>
+        <v>13638.97</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>14-188-CM26</t>
+          <t>577290-45-CM26</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -19810,12 +19814,12 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>61.979.750-7</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -19825,32 +19829,28 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
-        </is>
-      </c>
-      <c r="K301" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.770.640-k</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr"/>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>13638.97</v>
+        <v>2579.33</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>14-189-CM26</t>
+          <t>14-186-CM26</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -19909,13 +19909,13 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>3497.17</v>
+        <v>17602.43</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>14-190-CM26</t>
+          <t>14-187-CM26</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -19974,7 +19974,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>2797.74</v>
+        <v>17485.86</v>
       </c>
     </row>
     <row r="304">
@@ -20232,7 +20232,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>1261-28-CM26</t>
+          <t>14-195-CM26</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -20252,17 +20252,17 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>61.923.200-3</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -20272,12 +20272,12 @@
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.083.145-k</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
@@ -20291,13 +20291,13 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>14794.08</v>
+        <v>785.4</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>14-195-CM26</t>
+          <t>1261-28-CM26</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -20317,17 +20317,17 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>61.923.200-3</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -20337,12 +20337,12 @@
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
@@ -20356,7 +20356,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>785.4</v>
+        <v>14794.08</v>
       </c>
     </row>
     <row r="310">
@@ -20805,7 +20805,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>3553-166-CM26</t>
+          <t>750998-67-CM26</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -20825,17 +20825,17 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>61.402.000-8</t>
+          <t>69.255.100-1</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>I MUNICIPALIDAD DE LO ESPEJO</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -20864,13 +20864,13 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>196849.99</v>
+        <v>10567.2</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>750998-67-CM26</t>
+          <t>3553-166-CM26</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -20890,17 +20890,17 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>69.255.100-1</t>
+          <t>61.402.000-8</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LO ESPEJO</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -20929,7 +20929,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>10567.2</v>
+        <v>196849.99</v>
       </c>
     </row>
     <row r="319">
@@ -21325,7 +21325,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>1300-204-CM26</t>
+          <t>1602-64-SE26</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -21345,17 +21345,17 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>61.961.000-8</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL ADULTO MAYOR</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -21365,28 +21365,32 @@
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K325" t="inlineStr"/>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>76622.2</v>
+        <v>1719.43</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>1057492-2513-CM26</t>
+          <t>2790-194-CM26</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -21411,12 +21415,12 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>61.959.800-8</t>
+          <t>69.072.600-9</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>HOSPITAL ORIENTE DR LUIS TISNE BROUSSE</t>
+          <t>I MUNICIPALIDAD DE PAINE</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -21426,32 +21430,28 @@
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K326" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>76.854.651-7</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr"/>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>3169.62</v>
+        <v>17942.82</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>5768-102-CM26</t>
+          <t>1315526-15-CM26</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -21471,17 +21471,17 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>65.086.019-5</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>Centro Ideactiva</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -21491,12 +21491,12 @@
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
@@ -21510,13 +21510,13 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>54978</v>
+        <v>7692.76</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>2767-39-CM26</t>
+          <t>1368-34-CM26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -21541,12 +21541,12 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>69.072.000-0</t>
+          <t>75.980.060-5</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -21575,13 +21575,13 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>70764.53999999999</v>
+        <v>10769.86</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>1315526-15-CM26</t>
+          <t>5768-102-CM26</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -21601,17 +21601,17 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>65.086.019-5</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Centro Ideactiva</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -21621,12 +21621,12 @@
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
@@ -21640,13 +21640,13 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>7692.76</v>
+        <v>54978</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>1602-64-SE26</t>
+          <t>1057492-2513-CM26</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -21666,17 +21666,17 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>61.959.800-8</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>HOSPITAL ORIENTE DR LUIS TISNE BROUSSE</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -21686,17 +21686,17 @@
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
@@ -21705,13 +21705,13 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>1719.43</v>
+        <v>3169.62</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>1368-34-CM26</t>
+          <t>2767-39-CM26</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -21736,12 +21736,12 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>75.980.060-5</t>
+          <t>69.072.000-0</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -21770,13 +21770,13 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>10769.86</v>
+        <v>70764.53999999999</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2790-194-CM26</t>
+          <t>1300-204-CM26</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -21801,12 +21801,12 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>69.072.600-9</t>
+          <t>61.961.000-8</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAINE</t>
+          <t>SERVICIO NACIONAL DEL ADULTO MAYOR</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -21816,12 +21816,12 @@
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
+          <t>880443249</t>
         </is>
       </c>
       <c r="K332" t="inlineStr"/>
@@ -21831,13 +21831,13 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>17942.82</v>
+        <v>76622.2</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>798018-61-CM26</t>
+          <t>2674-576-CM26</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -21862,12 +21862,12 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>65.073.222-7</t>
+          <t>69.072.900-8</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -21877,17 +21877,17 @@
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
@@ -21896,13 +21896,13 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>5077.22</v>
+        <v>4226.17</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2674-576-CM26</t>
+          <t>2378-223-CM26</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -21927,12 +21927,12 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>69.072.900-8</t>
+          <t>69.070.700-4</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
+          <t>I MUNICIPALIDAD DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -21961,13 +21961,13 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>4226.17</v>
+        <v>1479.16</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>975-207-CM26</t>
+          <t>307-56-CM26</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -21987,17 +21987,17 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -22007,17 +22007,17 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
@@ -22026,13 +22026,13 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>1375.54</v>
+        <v>2113.08</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2021-131-CM26</t>
+          <t>798018-61-CM26</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -22052,17 +22052,17 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>61.101.040-0</t>
+          <t>65.073.222-7</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>ESTADO MAYOR CONJUNTO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -22072,12 +22072,12 @@
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
@@ -22091,13 +22091,13 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>21044.51</v>
+        <v>5077.22</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>307-56-CM26</t>
+          <t>975-207-CM26</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -22117,17 +22117,17 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -22137,17 +22137,17 @@
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K337" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
@@ -22156,13 +22156,13 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>2113.08</v>
+        <v>1375.54</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2378-223-CM26</t>
+          <t>2021-131-CM26</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -22182,17 +22182,17 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>69.070.700-4</t>
+          <t>61.101.040-0</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA FLORIDA</t>
+          <t>ESTADO MAYOR CONJUNTO</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -22202,17 +22202,17 @@
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
@@ -22221,7 +22221,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>1479.16</v>
+        <v>21044.51</v>
       </c>
     </row>
     <row r="339">
@@ -23393,7 +23393,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>1606-281-CM26</t>
+          <t>2732-21-CM26</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -23413,17 +23413,17 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>60.108.000-1</t>
+          <t>69.071.700-K</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>AGENCIA CHILENA DE COOPERACION INTERNACIONAL PARA EL DESARROLLO</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -23433,12 +23433,12 @@
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K357" t="inlineStr">
@@ -23452,7 +23452,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>6082.09</v>
+        <v>165430.94</v>
       </c>
     </row>
     <row r="358">
@@ -23523,7 +23523,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2732-21-CM26</t>
+          <t>1606-281-CM26</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -23543,17 +23543,17 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>69.071.700-K</t>
+          <t>60.108.000-1</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
+          <t>AGENCIA CHILENA DE COOPERACION INTERNACIONAL PARA EL DESARROLLO</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -23563,12 +23563,12 @@
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K359" t="inlineStr">
@@ -23582,7 +23582,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>165430.94</v>
+        <v>6082.09</v>
       </c>
     </row>
     <row r="360">
@@ -23783,7 +23783,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>604944-82-CM26</t>
+          <t>3894-65-CM26</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -23803,17 +23803,17 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>61.979.870-8</t>
+          <t>69.071.400-0</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DEFENSA</t>
+          <t>I MUNICIPALIDAD DE LAMPA</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -23823,12 +23823,12 @@
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K363" t="inlineStr">
@@ -23842,13 +23842,13 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>11132.26</v>
+        <v>64867.5</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>3894-65-CM26</t>
+          <t>595636-60-CM26</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -23873,12 +23873,12 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>69.071.400-0</t>
+          <t>61.312.000-9</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAMPA</t>
+          <t>INIA</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -23888,17 +23888,17 @@
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K364" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L364" t="inlineStr">
@@ -23907,13 +23907,13 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>64867.5</v>
+        <v>845.23</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>595636-60-CM26</t>
+          <t>604944-82-CM26</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -23933,17 +23933,17 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>61.312.000-9</t>
+          <t>61.979.870-8</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>INIA</t>
+          <t>SUBSECRETARIA DE DEFENSA</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -23953,17 +23953,17 @@
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K365" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
@@ -23972,13 +23972,13 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>845.23</v>
+        <v>11132.26</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>1237849-145-CM26</t>
+          <t>188-507-CM26</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -23998,17 +23998,17 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>65.081.056-2</t>
+          <t>70.933.700-9</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE FOMENTO AL DESARROLLO COMUNAL Y PRODUCTIVO DE LA FLORIDA</t>
+          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -24018,32 +24018,28 @@
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K366" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.854.651-7</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr"/>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>3077.1</v>
+        <v>34153</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>188-507-CM26</t>
+          <t>1271178-266-CM26</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -24063,17 +24059,17 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>70.933.700-9</t>
+          <t>71.369.900-4</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
+          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL DE MACUL</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -24083,28 +24079,32 @@
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
-        </is>
-      </c>
-      <c r="K367" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>34153</v>
+        <v>1479.16</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>1271178-266-CM26</t>
+          <t>1237849-145-CM26</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -24129,12 +24129,12 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>71.369.900-4</t>
+          <t>65.081.056-2</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL DE MACUL</t>
+          <t>CORPORACION MUNICIPAL DE FOMENTO AL DESARROLLO COMUNAL Y PRODUCTIVO DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
@@ -24144,17 +24144,17 @@
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K368" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L368" t="inlineStr">
@@ -24163,7 +24163,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>1479.16</v>
+        <v>3077.1</v>
       </c>
     </row>
     <row r="369">
@@ -24624,7 +24624,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>688-100-CM26</t>
+          <t>4246-85-CM26</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -24644,17 +24644,17 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>61.301.100-5</t>
+          <t>61.976.100-6</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>OFICINA DE ESTUDIOS Y POLITICAS AGRARIAS</t>
+          <t>SUPERINTENDENCIA DE CASINOS DE JUEGO</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -24664,12 +24664,12 @@
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K376" t="inlineStr">
@@ -24683,13 +24683,13 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>71574.92999999999</v>
+        <v>21128.69</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>4246-85-CM26</t>
+          <t>1375746-102-CM26</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -24714,12 +24714,12 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>61.976.100-6</t>
+          <t>61.981.280-8</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE CASINOS DE JUEGO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ACONCAGUA</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -24729,12 +24729,12 @@
       </c>
       <c r="I377" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J377" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K377" t="inlineStr">
@@ -24748,13 +24748,13 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>21128.69</v>
+        <v>16260.16</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>1375746-102-CM26</t>
+          <t>688-100-CM26</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -24774,17 +24774,17 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>61.981.280-8</t>
+          <t>61.301.100-5</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ACONCAGUA</t>
+          <t>OFICINA DE ESTUDIOS Y POLITICAS AGRARIAS</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -24794,12 +24794,12 @@
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K378" t="inlineStr">
@@ -24813,7 +24813,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>16260.16</v>
+        <v>71574.92999999999</v>
       </c>
     </row>
     <row r="379">
@@ -25144,7 +25144,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>2412-522-CM26</t>
+          <t>1260-126-SE26</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -25159,22 +25159,22 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>69.254.100-6</t>
+          <t>61.923.200-3</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LO PRADO</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -25184,17 +25184,17 @@
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>880443249</t>
         </is>
       </c>
       <c r="K384" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Extranjero</t>
         </is>
       </c>
       <c r="L384" t="inlineStr">
@@ -25203,13 +25203,13 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>74764.49000000001</v>
+        <v>106407.42</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>858-348-SE26</t>
+          <t>2412-522-CM26</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -25224,22 +25224,22 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.254.100-6</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE LO PRADO</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -25268,13 +25268,13 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>713286</v>
+        <v>74764.49000000001</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>867990-485-CM26</t>
+          <t>858-348-SE26</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -25294,17 +25294,17 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -25314,12 +25314,12 @@
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K386" t="inlineStr">
@@ -25333,13 +25333,13 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>224910</v>
+        <v>713286</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2412-528-CM26</t>
+          <t>867990-485-CM26</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -25349,27 +25349,27 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>69.254.100-6</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LO PRADO</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -25379,17 +25379,17 @@
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K387" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L387" t="inlineStr">
@@ -25398,13 +25398,13 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>10565.42</v>
+        <v>224910</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>604944-108-CM26</t>
+          <t>2412-528-CM26</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -25419,22 +25419,22 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>61.979.870-8</t>
+          <t>69.254.100-6</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DEFENSA</t>
+          <t>I MUNICIPALIDAD DE LO PRADO</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -25444,17 +25444,17 @@
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K388" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L388" t="inlineStr">
@@ -25463,13 +25463,13 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>8388.07</v>
+        <v>10565.42</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>587-431-CM26</t>
+          <t>604944-108-CM26</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -25484,7 +25484,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
@@ -25494,12 +25494,12 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>61.801.000-7</t>
+          <t>61.979.870-8</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>SUBSECRETARIA DE DEFENSA</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -25509,12 +25509,12 @@
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K389" t="inlineStr">
@@ -25528,13 +25528,13 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>13787.34</v>
+        <v>8388.07</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2733-421-CM26</t>
+          <t>587-431-CM26</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -25549,7 +25549,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
@@ -25559,12 +25559,12 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>69.071.700-K</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -25574,17 +25574,17 @@
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.334.381-2</t>
         </is>
       </c>
       <c r="K390" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L390" t="inlineStr">
@@ -25593,13 +25593,13 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>6339.25</v>
+        <v>13787.34</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>595636-75-CM26</t>
+          <t>2733-421-CM26</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -25614,7 +25614,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -25624,12 +25624,12 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>61.312.000-9</t>
+          <t>69.071.700-K</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>INIA</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
@@ -25639,17 +25639,17 @@
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K391" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L391" t="inlineStr">
@@ -25658,13 +25658,13 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>62978.85</v>
+        <v>6339.25</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2305-63-CM26</t>
+          <t>595636-75-CM26</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -25679,22 +25679,22 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>61.973.000-3</t>
+          <t>61.312.000-9</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>UNIDAD DE ANALISIS FINANCIERO</t>
+          <t>INIA</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
@@ -25704,12 +25704,12 @@
       </c>
       <c r="I392" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K392" t="inlineStr">
@@ -25723,13 +25723,13 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>5158.29</v>
+        <v>62978.85</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>2434-37-CM26</t>
+          <t>2305-63-CM26</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -25744,22 +25744,22 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>69.254.300-9</t>
+          <t>61.973.000-3</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
+          <t>UNIDAD DE ANALISIS FINANCIERO</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
@@ -25769,12 +25769,12 @@
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K393" t="inlineStr">
@@ -25788,7 +25788,7 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>120303.05</v>
+        <v>5158.29</v>
       </c>
     </row>
     <row r="394">
@@ -25859,7 +25859,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2981-1144-CM26</t>
+          <t>2434-37-CM26</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -25879,17 +25879,17 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>69.254.300-9</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -25899,12 +25899,12 @@
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K395" t="inlineStr">
@@ -25918,13 +25918,13 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>5772.69</v>
+        <v>120303.05</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>619284-146-CM26</t>
+          <t>2981-1144-CM26</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -25939,22 +25939,22 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>61.980.000-1</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TRANSPORTES</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -25964,12 +25964,12 @@
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K396" t="inlineStr">
@@ -25983,13 +25983,13 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>2751.09</v>
+        <v>5772.69</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>872-572-CM26</t>
+          <t>619284-146-CM26</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -26004,22 +26004,22 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>82.983.100-7</t>
+          <t>61.980.000-1</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>Comisión Chilena de Energía Nuclear</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
@@ -26029,12 +26029,12 @@
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>ORION 2000 SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>96.899.890-0</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K397" t="inlineStr">
@@ -26048,13 +26048,13 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>57068.83</v>
+        <v>2751.09</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>3363-94-CM26</t>
+          <t>872-572-CM26</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -26069,22 +26069,22 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>61.101.045-1</t>
+          <t>82.983.100-7</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>Comisión Chilena de Energía Nuclear</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -26094,12 +26094,12 @@
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>ORION 2000 SPA</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>96.899.890-0</t>
         </is>
       </c>
       <c r="K398" t="inlineStr">
@@ -26113,13 +26113,13 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>2498.75</v>
+        <v>57068.83</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>1533460-50-CM26</t>
+          <t>3363-94-CM26</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -26144,12 +26144,12 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>65.261.347-0</t>
+          <t>61.101.045-1</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>CORPORACIÓN MUNICIPAL DE CULTURA, DEPORTE Y DE FOMENTO DE DESARROLLO C</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
@@ -26159,12 +26159,12 @@
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.334.381-2</t>
         </is>
       </c>
       <c r="K399" t="inlineStr">
@@ -26178,13 +26178,13 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>3961.63</v>
+        <v>2498.75</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>1385462-180-CM26</t>
+          <t>1533460-50-CM26</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -26199,7 +26199,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
@@ -26209,12 +26209,12 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>65.261.347-0</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>CORPORACIÓN MUNICIPAL DE CULTURA, DEPORTE Y DE FOMENTO DE DESARROLLO C</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
@@ -26224,12 +26224,12 @@
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K400" t="inlineStr">
@@ -26243,13 +26243,13 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>6039.25</v>
+        <v>3961.63</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2341-499-CM26</t>
+          <t>1385462-180-CM26</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -26274,12 +26274,12 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>69.072.700-5</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
@@ -26289,28 +26289,32 @@
       </c>
       <c r="I401" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
-        </is>
-      </c>
-      <c r="K401" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>34986</v>
+        <v>6039.25</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>188-596-CM26</t>
+          <t>2341-499-CM26</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -26335,12 +26339,12 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>70.933.700-9</t>
+          <t>69.072.700-5</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
+          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
@@ -26350,32 +26354,28 @@
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
-        </is>
-      </c>
-      <c r="K402" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.854.651-7</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr"/>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>2235.26</v>
+        <v>34986</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>894778-42-CM26</t>
+          <t>188-596-CM26</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -26390,7 +26390,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
@@ -26400,12 +26400,12 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>60.501.000-8</t>
+          <t>70.933.700-9</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL INTERIOR</t>
+          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
@@ -26415,12 +26415,12 @@
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K403" t="inlineStr">
@@ -26434,13 +26434,13 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>332367</v>
+        <v>2235.26</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>1020-317-CM26</t>
+          <t>894778-42-CM26</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -26455,7 +26455,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
@@ -26465,12 +26465,12 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.501.000-8</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SUBSECRETARIA DEL INTERIOR</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
@@ -26480,12 +26480,12 @@
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K404" t="inlineStr">
@@ -26499,71 +26499,201 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>39342.59</v>
+        <v>332367</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
+          <t>894778-43-SE26</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>60.501.000-8</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL INTERIOR</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M405" s="2" t="n">
+        <v>30212.91</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>1020-317-CM26</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>XMS TECHNOLOGIES S.A.</t>
+        </is>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>76.083.145-k</t>
+        </is>
+      </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M406" s="2" t="n">
+        <v>39342.59</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
           <t>598-250-SE26</t>
         </is>
       </c>
-      <c r="B405" t="inlineStr">
-        <is>
-          <t>2239-11-LR24</t>
-        </is>
-      </c>
-      <c r="C405" t="inlineStr">
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
         <is>
           <t>sep-2026</t>
         </is>
       </c>
-      <c r="D405" t="inlineStr">
+      <c r="D407" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="E405" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F405" t="inlineStr">
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
         <is>
           <t>61.513.000-1</t>
         </is>
       </c>
-      <c r="G405" t="inlineStr">
+      <c r="G407" t="inlineStr">
         <is>
           <t>DIRECCION PREVISION DE CARABINEROS DE CHILE</t>
         </is>
       </c>
-      <c r="H405" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I405" t="inlineStr">
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
         <is>
           <t>Seidor Chile S.A.</t>
         </is>
       </c>
-      <c r="J405" t="inlineStr">
+      <c r="J407" t="inlineStr">
         <is>
           <t>96.986.170-4</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L405" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M405" s="2" t="n">
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M407" s="2" t="n">
         <v>340177.13</v>
       </c>
     </row>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/metropolitana.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/metropolitana.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M407"/>
+  <dimension ref="A1:M421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1351,7 +1351,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>633-132-CM25</t>
+          <t>188-120-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1371,17 +1371,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>70.933.700-9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1391,12 +1391,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1410,13 +1410,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>23090.76</v>
+        <v>9246.299999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>188-120-CM25</t>
+          <t>633-132-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1436,17 +1436,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>70.933.700-9</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>9246.299999999999</v>
+        <v>23090.76</v>
       </c>
     </row>
     <row r="17">
@@ -1611,7 +1611,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5768-38-CM25</t>
+          <t>2673-44-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.072.900-8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1651,12 +1651,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1670,13 +1670,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>27555.64</v>
+        <v>99781.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2673-44-CM25</t>
+          <t>5768-38-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1696,17 +1696,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.072.900-8</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1716,12 +1716,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>99781.5</v>
+        <v>27555.64</v>
       </c>
     </row>
     <row r="21">
@@ -2062,7 +2062,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3323-21-CM25</t>
+          <t>4388-49-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2087,12 +2087,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>60.511.000-2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SUBSECRETARIA DEL INTERIOR</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2121,13 +2121,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>888.7</v>
+        <v>15440.27</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4388-49-CM25</t>
+          <t>3323-21-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>60.511.000-2</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL INTERIOR</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2186,7 +2186,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>15440.27</v>
+        <v>888.7</v>
       </c>
     </row>
     <row r="28">
@@ -2582,7 +2582,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>577290-60-CM25</t>
+          <t>577290-59-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2641,13 +2641,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1213.8</v>
+        <v>10340.56</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>577290-59-CM25</t>
+          <t>577290-60-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2687,12 +2687,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>10340.56</v>
+        <v>1213.8</v>
       </c>
     </row>
     <row r="36">
@@ -2842,7 +2842,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>606-153-CM25</t>
+          <t>4499-56-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>60.513.000-3</t>
+          <t>69.073.100-2</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2882,12 +2882,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>ORION 2000 SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>96.899.890-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2901,13 +2901,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>61145.18</v>
+        <v>14164.33</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4499-56-CM25</t>
+          <t>606-153-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2932,12 +2932,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.073.100-2</t>
+          <t>60.513.000-3</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO</t>
+          <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2947,12 +2947,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>ORION 2000 SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.899.890-0</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>14164.33</v>
+        <v>61145.18</v>
       </c>
     </row>
     <row r="40">
@@ -3228,7 +3228,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1736-2942-CM25</t>
+          <t>1300-226-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3248,17 +3248,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.255.300-4</t>
+          <t>61.961.000-8</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA COMUNA DE EL BOSQUE</t>
+          <t>SERVICIO NACIONAL DEL ADULTO MAYOR</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3268,12 +3268,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>GTD TELEDUCTOS S.A</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>88.983.600-8</t>
+          <t>880443249</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3283,13 +3283,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>757.61</v>
+        <v>59336.26</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1300-226-CM25</t>
+          <t>1736-2942-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3309,17 +3309,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.961.000-8</t>
+          <t>69.255.300-4</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL ADULTO MAYOR</t>
+          <t>I MUNICIPALIDAD DE LA COMUNA DE EL BOSQUE</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>GTD TELEDUCTOS S.A</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>880443249</t>
+          <t>88.983.600-8</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3344,13 +3344,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>59336.26</v>
+        <v>757.61</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4928-33-CM25</t>
+          <t>4928-38-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3409,13 +3409,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>6133.81</v>
+        <v>5076.25</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4928-38-CM25</t>
+          <t>4928-33-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3474,7 +3474,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>5076.25</v>
+        <v>6133.81</v>
       </c>
     </row>
     <row r="48">
@@ -4455,7 +4455,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1057473-261-CM25</t>
+          <t>798018-37-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.999.030-7</t>
+          <t>65.073.222-7</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Centro Metropolitano de Atención Prehospitalaria</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4514,13 +4514,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>70821.66</v>
+        <v>4356.66</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>798018-37-CM25</t>
+          <t>1057473-261-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>65.073.222-7</t>
+          <t>61.999.030-7</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>Centro Metropolitano de Atención Prehospitalaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4579,7 +4579,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>4356.66</v>
+        <v>70821.66</v>
       </c>
     </row>
     <row r="65">
@@ -5093,7 +5093,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2767-59-CM25</t>
+          <t>2770-168-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>69.072.000-0</t>
+          <t>69.070.900-7</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
+          <t>I MUNICIPALIDAD DE MAIPU</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5133,32 +5133,28 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>70821.66</v>
+        <v>407446.96</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2770-168-CM25</t>
+          <t>2767-59-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5183,12 +5179,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>69.070.900-7</t>
+          <t>69.072.000-0</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAIPU</t>
+          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5198,22 +5194,26 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>407446.96</v>
+        <v>70821.66</v>
       </c>
     </row>
     <row r="75">
@@ -5284,7 +5284,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5684-339-CM25</t>
+          <t>711841-374-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5304,17 +5304,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.103.000-4</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>ORION 2000 SPA</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>96.899.890-0</t>
+          <t>76.083.145-k</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5343,13 +5343,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>2608.86</v>
+        <v>9127.42</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>711841-374-CM25</t>
+          <t>5684-339-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5369,17 +5369,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>60.103.000-4</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5389,12 +5389,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>ORION 2000 SPA</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
+          <t>96.899.890-0</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5408,7 +5408,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>9127.42</v>
+        <v>2608.86</v>
       </c>
     </row>
     <row r="78">
@@ -6251,7 +6251,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1375761-49-CM25</t>
+          <t>857-137-CM25</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61.981.330-8</t>
+          <t>72.576.700-5</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
+          <t>SERVICIO NACIONAL DE LA DISCAPACIDAD</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6291,12 +6291,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6310,13 +6310,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>13423.2</v>
+        <v>50799.67</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>857-137-CM25</t>
+          <t>1232911-50-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>72.576.700-5</t>
+          <t>65.115.629-7</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE LA DISCAPACIDAD</t>
+          <t>Corporación Municipal de Deportes de Colina</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6375,13 +6375,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>50799.67</v>
+        <v>7812.11</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1232911-50-CM25</t>
+          <t>1375761-49-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6406,12 +6406,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>65.115.629-7</t>
+          <t>61.981.330-8</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Deportes de Colina</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6421,12 +6421,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6440,13 +6440,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>7812.11</v>
+        <v>13423.2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>4928-63-CM25</t>
+          <t>3328-2176-CM25</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6486,12 +6486,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6505,13 +6505,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>14805.74</v>
+        <v>1201.16</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>3328-2176-CM25</t>
+          <t>3328-2174-CM25</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6570,13 +6570,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>1201.16</v>
+        <v>8460.42</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1051173-52-CM25</t>
+          <t>4928-63-CM25</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6601,12 +6601,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>60.100.003-2</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>MINISTERIO SECRETARIA GENERAL DE LA PRESIDENCIA DE LA REPUBLICA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6616,28 +6616,32 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>74403.8</v>
+        <v>14805.74</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>3328-2174-CM25</t>
+          <t>1051173-52-CM25</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6662,12 +6666,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>60.100.003-2</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>MINISTERIO SECRETARIA GENERAL DE LA PRESIDENCIA DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6677,26 +6681,22 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>8460.42</v>
+        <v>74403.8</v>
       </c>
     </row>
     <row r="98">
@@ -7539,7 +7539,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1415862-61-CM25</t>
+          <t>539119-4751-CM25</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7564,12 +7564,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>61.533.000-0</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7579,12 +7579,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -7598,13 +7598,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>15946</v>
+        <v>5076.25</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>539119-4751-CM25</t>
+          <t>1415862-61-CM25</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>61.533.000-0</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>77.553.790-6</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -7663,7 +7663,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>5076.25</v>
+        <v>15946</v>
       </c>
     </row>
     <row r="113">
@@ -7799,7 +7799,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2378-90-CM25</t>
+          <t>1271178-278-CM25</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7824,12 +7824,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>69.070.700-4</t>
+          <t>71.369.900-4</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA FLORIDA</t>
+          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL DE MACUL</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7839,17 +7839,17 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7858,13 +7858,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>68311.71000000001</v>
+        <v>3172.66</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1271178-278-CM25</t>
+          <t>2378-90-CM25</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7889,12 +7889,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>71.369.900-4</t>
+          <t>69.070.700-4</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL DE MACUL</t>
+          <t>I MUNICIPALIDAD DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7904,17 +7904,17 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7923,7 +7923,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>3172.66</v>
+        <v>68311.71000000001</v>
       </c>
     </row>
     <row r="117">
@@ -7990,7 +7990,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>3363-94-CM25</t>
+          <t>2412-807-CM25</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -8015,12 +8015,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>61.101.045-1</t>
+          <t>69.254.100-6</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE LO PRADO</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -8030,17 +8030,17 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8049,13 +8049,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>2115.11</v>
+        <v>63983.44</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2412-807-CM25</t>
+          <t>3363-94-CM25</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>69.254.100-6</t>
+          <t>61.101.045-1</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LO PRADO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -8095,17 +8095,17 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8114,13 +8114,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>63983.44</v>
+        <v>2115.11</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>688-173-CM25</t>
+          <t>1057494-8528-CM25</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -8140,17 +8140,17 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>61.301.100-5</t>
+          <t>61.608.102-0</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>OFICINA DE ESTUDIOS Y POLITICAS AGRARIAS</t>
+          <t>SERVICIO DE SALUD SUR HOSPITAL EXEQUIEL</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -8160,26 +8160,22 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>71582.07000000001</v>
+        <v>71651.33</v>
       </c>
     </row>
     <row r="121">
@@ -8250,7 +8246,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1057494-8528-CM25</t>
+          <t>688-173-CM25</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8270,17 +8266,17 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>61.608.102-0</t>
+          <t>61.301.100-5</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD SUR HOSPITAL EXEQUIEL</t>
+          <t>OFICINA DE ESTUDIOS Y POLITICAS AGRARIAS</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -8290,22 +8286,26 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr"/>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>71651.33</v>
+        <v>71582.07000000001</v>
       </c>
     </row>
     <row r="123">
@@ -9270,7 +9270,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1076403-37-CM25</t>
+          <t>1607-191-CM25</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9295,12 +9295,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>60.601.000-1</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
+          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -9310,12 +9310,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -9329,7 +9329,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>891357.6</v>
+        <v>53878.44</v>
       </c>
     </row>
     <row r="139">
@@ -9400,7 +9400,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1607-191-CM25</t>
+          <t>1076403-37-CM25</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9425,12 +9425,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>60.601.000-1</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
+          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -9440,12 +9440,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.553.790-6</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -9459,7 +9459,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>53878.44</v>
+        <v>891357.6</v>
       </c>
     </row>
     <row r="141">
@@ -9530,7 +9530,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>872-551-CM25</t>
+          <t>587-657-CM25</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>82.983.100-7</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Comisión Chilena de Energía Nuclear</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9570,12 +9570,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>ORION 2000 SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>96.899.890-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -9589,13 +9589,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>57068.83</v>
+        <v>14172.9</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>519302-150-CM25</t>
+          <t>872-551-CM25</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>65.999.669-3</t>
+          <t>82.983.100-7</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE PROPIEDAD INDUSTRIAL</t>
+          <t>Comisión Chilena de Energía Nuclear</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>ORION 2000 SPA</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.899.890-0</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -9654,13 +9654,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>10150.22</v>
+        <v>57068.83</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>587-657-CM25</t>
+          <t>519302-150-CM25</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.801.000-7</t>
+          <t>65.999.669-3</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>INSTITUTO NACIONAL DE PROPIEDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>14172.9</v>
+        <v>10150.22</v>
       </c>
     </row>
     <row r="145">
@@ -9985,7 +9985,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1216094-117-CM25</t>
+          <t>2703-1163-CM25</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -10010,12 +10010,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>60.801.000-9</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -10025,17 +10025,17 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -10044,7 +10044,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>7389.04</v>
+        <v>6343.89</v>
       </c>
     </row>
     <row r="150">
@@ -10111,7 +10111,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2703-1163-CM25</t>
+          <t>1216094-117-CM25</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -10136,12 +10136,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.801.000-9</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -10151,17 +10151,17 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -10170,13 +10170,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>6343.89</v>
+        <v>7389.04</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1057501-24877-CM25</t>
+          <t>608897-11250-CM25</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -10196,17 +10196,17 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.979.930-5</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -10216,28 +10216,32 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>67173.12</v>
+        <v>9727.92</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>608897-11250-CM25</t>
+          <t>1019-548-CM25</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -10262,12 +10266,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>61.979.930-5</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -10296,13 +10300,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>9727.92</v>
+        <v>4863.77</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1019-548-CM25</t>
+          <t>1019-549-CM25</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -10342,32 +10346,28 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>4863.77</v>
+        <v>73666.52</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1019-549-CM25</t>
+          <t>1057501-24877-CM25</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -10387,17 +10387,17 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -10422,7 +10422,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>73666.52</v>
+        <v>67173.12</v>
       </c>
     </row>
     <row r="156">
@@ -10684,7 +10684,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1020-454-CM25</t>
+          <t>1057500-626-CM25</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10704,17 +10704,17 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.608.500-K</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR ORIENTE</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10724,32 +10724,28 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>245698.11</v>
+        <v>67173.12</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1057500-626-CM25</t>
+          <t>1450519-14-CM25</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10769,17 +10765,17 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>61.608.500-K</t>
+          <t>61.999.390-K</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR ORIENTE</t>
+          <t>SUBSECRETARIA DE SEGURIDAD PUBLICA</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10789,28 +10785,32 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K161" t="inlineStr"/>
+          <t>76.334.381-2</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>67173.12</v>
+        <v>5787.03</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1450519-14-CM25</t>
+          <t>1020-454-CM25</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10835,12 +10835,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>61.999.390-K</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SEGURIDAD PUBLICA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -10869,7 +10869,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>5787.03</v>
+        <v>245698.11</v>
       </c>
     </row>
     <row r="163">
@@ -11265,7 +11265,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1426104-134-CM25</t>
+          <t>1425525-63-CM25</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11285,17 +11285,17 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>62.000.560-6</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>AGENCIA NACIONAL DE CIBERSEGURIDAD</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -11305,28 +11305,32 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Site Chile Sociedad Anónima</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>96.988.790-8</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>4641</v>
+        <v>13176.28</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1425525-63-CM25</t>
+          <t>1426104-134-CM25</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11346,17 +11350,17 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>62.000.560-6</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>AGENCIA NACIONAL DE CIBERSEGURIDAD</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -11366,26 +11370,22 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Site Chile Sociedad Anónima</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.988.790-8</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>13176.28</v>
+        <v>4641</v>
       </c>
     </row>
     <row r="171">
@@ -11708,7 +11708,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>761-719-CM25</t>
+          <t>872-615-CM25</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11728,17 +11728,17 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>60.515.000-4</t>
+          <t>82.983.100-7</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
+          <t>Comisión Chilena de Energía Nuclear</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11748,17 +11748,17 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>XERTICA CHILE SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>77.223.453-8</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -11767,13 +11767,13 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>100143.74</v>
+        <v>2326.09</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>514862-1032-CM25</t>
+          <t>761-719-CM25</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11793,17 +11793,17 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>71.234.100-9</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE PENALOLEN PARA EL DESARROLO SOCIAL CORMUP</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>SEIDOR TECHNOLOGIES S.A.</t>
+          <t>XERTICA CHILE SPA</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>76.449.580-2</t>
+          <t>77.223.453-8</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -11832,13 +11832,13 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>129944.43</v>
+        <v>100143.74</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>872-615-CM25</t>
+          <t>514862-1032-CM25</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11863,12 +11863,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>82.983.100-7</t>
+          <t>71.234.100-9</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Comisión Chilena de Energía Nuclear</t>
+          <t>CORPORACION MUNICIPAL DE PENALOLEN PARA EL DESARROLO SOCIAL CORMUP</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11878,17 +11878,17 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>SEIDOR TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.449.580-2</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -11897,7 +11897,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>2326.09</v>
+        <v>129944.43</v>
       </c>
     </row>
     <row r="179">
@@ -12878,7 +12878,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>628-490-CM25</t>
+          <t>628-440-CM25</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12918,12 +12918,12 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>XERTICA CHILE SPA</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>77.223.453-8</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -12937,13 +12937,13 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>6678.28</v>
+        <v>94180.98</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>870-391-CM25</t>
+          <t>628-483-CM25</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12968,12 +12968,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>60.718.000-8</t>
+          <t>60.107.000-6</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>COMISION NACIONAL DE RIEGO</t>
+          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -13002,13 +13002,13 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>3078.29</v>
+        <v>21145.11</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>628-440-CM25</t>
+          <t>870-391-CM25</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -13033,12 +13033,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>60.107.000-6</t>
+          <t>60.718.000-8</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
+          <t>COMISION NACIONAL DE RIEGO</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -13048,12 +13048,12 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>XERTICA CHILE SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>77.223.453-8</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -13067,13 +13067,13 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>94180.98</v>
+        <v>3078.29</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>628-483-CM25</t>
+          <t>628-490-CM25</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -13132,13 +13132,13 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>21145.11</v>
+        <v>6678.28</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1057468-288-CM25</t>
+          <t>2580-1346-CM25</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -13163,12 +13163,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>61.608.600-6</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO CENTRAL</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -13178,12 +13178,12 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>92.580.000-7</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -13197,13 +13197,13 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>13321.42</v>
+        <v>6236.36</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1121-150-CM25</t>
+          <t>1057468-288-CM25</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -13228,12 +13228,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>61.706.000-0</t>
+          <t>61.608.600-6</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Comisión Chilena del Cobre - COCHILCO</t>
+          <t>SERVICIO DE SALUD METROPOLITANO CENTRAL</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -13243,12 +13243,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -13262,13 +13262,13 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>3611.55</v>
+        <v>13321.42</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1260-280-CM25</t>
+          <t>1121-150-CM25</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -13293,12 +13293,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>61.923.200-3</t>
+          <t>61.706.000-0</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -13327,13 +13327,13 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>5159.36</v>
+        <v>3611.55</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2580-1346-CM25</t>
+          <t>1260-280-CM25</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -13358,12 +13358,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>61.923.200-3</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -13373,12 +13373,12 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -13392,7 +13392,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>6236.36</v>
+        <v>5159.36</v>
       </c>
     </row>
     <row r="202">
@@ -13979,7 +13979,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>979-2352-CM25</t>
+          <t>858-808-CM25</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13999,17 +13999,17 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -14019,12 +14019,12 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -14038,13 +14038,13 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>70870.64</v>
+        <v>75372.16</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>858-808-CM25</t>
+          <t>979-2352-CM25</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -14064,17 +14064,17 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -14084,12 +14084,12 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.334.381-2</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -14103,7 +14103,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>75372.16</v>
+        <v>70870.64</v>
       </c>
     </row>
     <row r="213">
@@ -14499,7 +14499,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1057491-21303-CM25</t>
+          <t>1385462-330-CM25</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -14519,17 +14519,17 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>61.608.408-9</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -14539,12 +14539,12 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>SEIDOR TECHNOLOGIES S.A.</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>76.449.580-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
@@ -14558,13 +14558,13 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>99960</v>
+        <v>22983.66</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1385462-330-CM25</t>
+          <t>1057491-21303-CM25</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -14584,17 +14584,17 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>61.608.408-9</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -14604,12 +14604,12 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>SEIDOR TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.449.580-2</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -14623,7 +14623,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>22983.66</v>
+        <v>99960</v>
       </c>
     </row>
     <row r="221">
@@ -15604,7 +15604,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>1020-29-CM26</t>
+          <t>2934-12-CM26</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -15624,17 +15624,17 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.073.200-9</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE ALHUE</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -15663,13 +15663,13 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>46156.53</v>
+        <v>4435.13</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2934-12-CM26</t>
+          <t>1020-29-CM26</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -15689,17 +15689,17 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>69.073.200-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALHUE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -15728,7 +15728,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>4435.13</v>
+        <v>46156.53</v>
       </c>
     </row>
     <row r="238">
@@ -15925,7 +15925,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>539119-470-CM26</t>
+          <t>1238177-14-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15950,12 +15950,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>65.165.009-7</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SEGURIDAD CIUDADANA</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -15965,12 +15965,12 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
@@ -15984,13 +15984,13 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>1056.9</v>
+        <v>3534.3</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1238177-14-CM26</t>
+          <t>539119-470-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -16015,12 +16015,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>65.165.009-7</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SEGURIDAD CIUDADANA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -16030,12 +16030,12 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
@@ -16049,7 +16049,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>3534.3</v>
+        <v>1056.9</v>
       </c>
     </row>
     <row r="243">
@@ -17083,7 +17083,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>1388961-131-CM26</t>
+          <t>1386073-60-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -17103,17 +17103,17 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>65.118.035-K</t>
+          <t>71.004.200-4</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>ASOCIACION DE MUNICIPALIDADES PARA LA SEGURIDAD CIUDADANA EN LA ZONA ORIENTE</t>
+          <t>CORP CULTURAL DE LAS CONDES</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -17123,28 +17123,32 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>ASESORIAS EN INFORMATICA ZONA-TI LIMITADA</t>
+          <t>SUPER SOFTWARE SPA</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>76.338.883-2</t>
-        </is>
-      </c>
-      <c r="K259" t="inlineStr"/>
+          <t>76.486.150-7</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>6417.17</v>
+        <v>15244.28</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>1386073-60-CM26</t>
+          <t>1388961-131-CM26</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -17164,17 +17168,17 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>71.004.200-4</t>
+          <t>65.118.035-K</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>CORP CULTURAL DE LAS CONDES</t>
+          <t>ASOCIACION DE MUNICIPALIDADES PARA LA SEGURIDAD CIUDADANA EN LA ZONA ORIENTE</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -17184,26 +17188,22 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>SUPER SOFTWARE SPA</t>
+          <t>ASESORIAS EN INFORMATICA ZONA-TI LIMITADA</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>76.486.150-7</t>
-        </is>
-      </c>
-      <c r="K260" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.338.883-2</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr"/>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>15244.28</v>
+        <v>6417.17</v>
       </c>
     </row>
     <row r="261">
@@ -17339,7 +17339,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>1002584-128-CM26</t>
+          <t>1300026-9-CM26</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -17359,17 +17359,17 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>65.154.016-k</t>
+          <t>65.497.180-3</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>DIRECCION DE EDUCACION PUBLICA</t>
+          <t>CORP CULTURAL DE LA COMUNA DE LA GRANJA</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -17379,12 +17379,12 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
@@ -17398,13 +17398,13 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>114494.66</v>
+        <v>1774.05</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>1300026-9-CM26</t>
+          <t>1002584-128-CM26</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -17424,17 +17424,17 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>65.497.180-3</t>
+          <t>65.154.016-k</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>CORP CULTURAL DE LA COMUNA DE LA GRANJA</t>
+          <t>DIRECCION DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -17444,12 +17444,12 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.334.381-2</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
@@ -17463,13 +17463,13 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>1774.05</v>
+        <v>114494.66</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>1592-28-CM26</t>
+          <t>3654-91-CM26</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -17489,17 +17489,17 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>61.503.000-7</t>
+          <t>61.101.034-6</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE PREVISION SOCIAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -17509,12 +17509,12 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
@@ -17528,7 +17528,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>16439.18</v>
+        <v>18147.5</v>
       </c>
     </row>
     <row r="266">
@@ -17599,7 +17599,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>3654-91-CM26</t>
+          <t>1592-28-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -17619,17 +17619,17 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>61.101.034-6</t>
+          <t>61.503.000-7</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SUBSECRETARIA DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -17639,12 +17639,12 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.334.381-2</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
@@ -17658,13 +17658,13 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>18147.5</v>
+        <v>16439.18</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>975-101-CM26</t>
+          <t>975-102-CM26</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -17704,32 +17704,28 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
-        </is>
-      </c>
-      <c r="K268" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.770.640-k</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr"/>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>224533.9</v>
+        <v>4470.83</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>975-102-CM26</t>
+          <t>975-101-CM26</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -17769,22 +17765,26 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>79.770.640-k</t>
-        </is>
-      </c>
-      <c r="K269" t="inlineStr"/>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>4470.83</v>
+        <v>224533.9</v>
       </c>
     </row>
     <row r="270">
@@ -17851,7 +17851,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>4294-60-CM26</t>
+          <t>1216088-95-CM26</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -17876,12 +17876,12 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>65.077.010-2</t>
+          <t>65.065.121-9</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES DE PUENTE ALTO</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -17891,17 +17891,17 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -17910,13 +17910,13 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>14794.08</v>
+        <v>845.38</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>1216088-95-CM26</t>
+          <t>4294-60-CM26</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -17941,12 +17941,12 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>65.065.121-9</t>
+          <t>65.077.010-2</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES DE PUENTE ALTO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -17956,17 +17956,17 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -17975,7 +17975,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>845.38</v>
+        <v>14794.08</v>
       </c>
     </row>
     <row r="273">
@@ -18371,7 +18371,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2580-175-CM26</t>
+          <t>610-21-CM26</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -18396,12 +18396,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>61.707.000-6</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>Comisión Nacional de Energía</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -18411,28 +18411,32 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
-        </is>
-      </c>
-      <c r="K279" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>15856.75</v>
+        <v>2941.38</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>610-21-CM26</t>
+          <t>2580-175-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -18457,12 +18461,12 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>61.707.000-6</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Comisión Nacional de Energía</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -18472,32 +18476,28 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K280" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.854.651-7</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>2941.38</v>
+        <v>15856.75</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>699360-19-CM26</t>
+          <t>2343-162-CM26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -18522,12 +18522,12 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>60.505.000-k</t>
+          <t>69.070.100-6</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE SANTIAGO</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -18537,17 +18537,17 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
@@ -18556,13 +18556,13 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>4325.59</v>
+        <v>2536.13</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2343-162-CM26</t>
+          <t>1428670-72-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -18582,17 +18582,17 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>69.070.100-6</t>
+          <t>65.117.794-4</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTIAGO</t>
+          <t>ASOCIACION METROPOLITANA DE MUNICIPALIDADES DE SANTIAGO SUR PARA LA GE</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -18602,32 +18602,28 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K282" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>79.770.640-k</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr"/>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>2536.13</v>
+        <v>9507.48</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>1428670-72-CM26</t>
+          <t>699360-19-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -18647,17 +18643,17 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>65.117.794-4</t>
+          <t>60.505.000-k</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>ASOCIACION METROPOLITANA DE MUNICIPALIDADES DE SANTIAGO SUR PARA LA GE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -18667,22 +18663,26 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>79.770.640-k</t>
-        </is>
-      </c>
-      <c r="K283" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>9507.48</v>
+        <v>4325.59</v>
       </c>
     </row>
     <row r="284">
@@ -18753,7 +18753,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>5684-256-CM26</t>
+          <t>4928-38-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -18778,12 +18778,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -18793,12 +18793,12 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
@@ -18812,13 +18812,13 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>2461.68</v>
+        <v>4617.6</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>4928-38-CM26</t>
+          <t>5684-256-CM26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -18843,12 +18843,12 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -18858,12 +18858,12 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
@@ -18877,7 +18877,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>4617.6</v>
+        <v>2461.68</v>
       </c>
     </row>
     <row r="287">
@@ -18948,7 +18948,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>1020-136-CM26</t>
+          <t>1238177-77-CM26</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -18968,17 +18968,17 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>65.165.009-7</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SEGURIDAD CIUDADANA</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -19007,13 +19007,13 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>2579.15</v>
+        <v>1031.66</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>1238177-77-CM26</t>
+          <t>1020-136-CM26</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -19033,17 +19033,17 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>65.165.009-7</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SEGURIDAD CIUDADANA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -19072,13 +19072,13 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>1031.66</v>
+        <v>2579.15</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>872-222-CM26</t>
+          <t>1018-58-CM26</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -19098,17 +19098,17 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>82.983.100-7</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Comisión Chilena de Energía Nuclear</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -19118,32 +19118,28 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K290" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr"/>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>8453.76</v>
+        <v>55977.6</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>1018-58-CM26</t>
+          <t>872-222-CM26</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -19163,17 +19159,17 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>82.983.100-7</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Comisión Chilena de Energía Nuclear</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -19183,22 +19179,26 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K291" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>55977.6</v>
+        <v>8453.76</v>
       </c>
     </row>
     <row r="292">
@@ -19399,7 +19399,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2483-191-CM26</t>
+          <t>3838-123-CM26</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -19419,17 +19419,17 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>69.071.300-4</t>
+          <t>69.090.600-7</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILICURA</t>
+          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -19439,12 +19439,12 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
@@ -19458,13 +19458,13 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>61542.04</v>
+        <v>4226.88</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>3838-123-CM26</t>
+          <t>2483-191-CM26</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -19484,17 +19484,17 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>69.090.600-7</t>
+          <t>69.071.300-4</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
+          <t>I MUNICIPALIDAD DE QUILICURA</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -19504,12 +19504,12 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
@@ -19523,7 +19523,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>4226.88</v>
+        <v>61542.04</v>
       </c>
     </row>
     <row r="297">
@@ -19594,7 +19594,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>14-189-CM26</t>
+          <t>14-186-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -19653,13 +19653,13 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>3497.17</v>
+        <v>17602.43</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>14-190-CM26</t>
+          <t>14-187-CM26</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -19718,7 +19718,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>2797.74</v>
+        <v>17485.86</v>
       </c>
     </row>
     <row r="300">
@@ -19850,7 +19850,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>14-186-CM26</t>
+          <t>14-190-CM26</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -19909,13 +19909,13 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>17602.43</v>
+        <v>2797.74</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>14-187-CM26</t>
+          <t>14-189-CM26</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -19974,7 +19974,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>17485.86</v>
+        <v>3497.17</v>
       </c>
     </row>
     <row r="304">
@@ -20232,7 +20232,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>14-195-CM26</t>
+          <t>1261-28-CM26</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -20252,17 +20252,17 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>61.923.200-3</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -20272,12 +20272,12 @@
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
@@ -20291,13 +20291,13 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>785.4</v>
+        <v>14794.08</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>1261-28-CM26</t>
+          <t>14-195-CM26</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -20317,17 +20317,17 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>61.923.200-3</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -20337,12 +20337,12 @@
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.083.145-k</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
@@ -20356,7 +20356,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>14794.08</v>
+        <v>785.4</v>
       </c>
     </row>
     <row r="310">
@@ -20549,7 +20549,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>705290-1047-CM26</t>
+          <t>2793-487-CM26</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -20569,17 +20569,17 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>61.608.205-1</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD OCCIDENTE HOSPITAL DR FELIX BULNES CERDA</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -20608,7 +20608,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>44351.3</v>
+        <v>402884.5</v>
       </c>
     </row>
     <row r="314">
@@ -20679,7 +20679,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2793-487-CM26</t>
+          <t>705290-1047-CM26</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -20699,17 +20699,17 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>61.608.205-1</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Municipalidad de Huechuraba</t>
+          <t>SERVICIO SALUD OCCIDENTE HOSPITAL DR FELIX BULNES CERDA</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -20738,7 +20738,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>402884.5</v>
+        <v>44351.3</v>
       </c>
     </row>
     <row r="316">
@@ -21516,7 +21516,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>1368-34-CM26</t>
+          <t>5768-102-CM26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -21536,17 +21536,17 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>75.980.060-5</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -21556,12 +21556,12 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
@@ -21575,13 +21575,13 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>10769.86</v>
+        <v>54978</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>5768-102-CM26</t>
+          <t>1057492-2513-CM26</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -21606,12 +21606,12 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.959.800-8</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>HOSPITAL ORIENTE DR LUIS TISNE BROUSSE</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -21621,17 +21621,17 @@
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
@@ -21640,13 +21640,13 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>54978</v>
+        <v>3169.62</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>1057492-2513-CM26</t>
+          <t>2767-39-CM26</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -21666,17 +21666,17 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>61.959.800-8</t>
+          <t>69.072.000-0</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>HOSPITAL ORIENTE DR LUIS TISNE BROUSSE</t>
+          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -21686,17 +21686,17 @@
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
@@ -21705,13 +21705,13 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>3169.62</v>
+        <v>70764.53999999999</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>2767-39-CM26</t>
+          <t>1300-204-CM26</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -21731,17 +21731,17 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>69.072.000-0</t>
+          <t>61.961.000-8</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
+          <t>SERVICIO NACIONAL DEL ADULTO MAYOR</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -21751,32 +21751,28 @@
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K331" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr"/>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>70764.53999999999</v>
+        <v>76622.2</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>1300-204-CM26</t>
+          <t>1368-34-CM26</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -21796,17 +21792,17 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>61.961.000-8</t>
+          <t>75.980.060-5</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL ADULTO MAYOR</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -21816,28 +21812,32 @@
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K332" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>76622.2</v>
+        <v>10769.86</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2674-576-CM26</t>
+          <t>2378-223-CM26</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -21862,12 +21862,12 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>69.072.900-8</t>
+          <t>69.070.700-4</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
+          <t>I MUNICIPALIDAD DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -21896,13 +21896,13 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>4226.17</v>
+        <v>1479.16</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2378-223-CM26</t>
+          <t>307-56-CM26</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -21927,12 +21927,12 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>69.070.700-4</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA FLORIDA</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -21961,13 +21961,13 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>1479.16</v>
+        <v>2113.08</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>307-56-CM26</t>
+          <t>2021-131-CM26</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -21987,17 +21987,17 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>61.101.040-0</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>ESTADO MAYOR CONJUNTO</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -22007,17 +22007,17 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
@@ -22026,13 +22026,13 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>2113.08</v>
+        <v>21044.51</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>798018-61-CM26</t>
+          <t>975-207-CM26</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -22052,17 +22052,17 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>65.073.222-7</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -22072,12 +22072,12 @@
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
@@ -22091,13 +22091,13 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>5077.22</v>
+        <v>1375.54</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>975-207-CM26</t>
+          <t>2674-576-CM26</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -22117,17 +22117,17 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.072.900-8</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -22137,17 +22137,17 @@
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K337" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
@@ -22156,13 +22156,13 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>1375.54</v>
+        <v>4226.17</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2021-131-CM26</t>
+          <t>798018-61-CM26</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -22182,17 +22182,17 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>61.101.040-0</t>
+          <t>65.073.222-7</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>ESTADO MAYOR CONJUNTO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -22202,12 +22202,12 @@
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
@@ -22221,13 +22221,13 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>21044.51</v>
+        <v>5077.22</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>699360-38-CM26</t>
+          <t>539119-2289-CM26</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -22247,12 +22247,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>60.505.000-k</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
@@ -22267,17 +22267,17 @@
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
@@ -22286,13 +22286,13 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>4587.2</v>
+        <v>845.23</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>539119-2289-CM26</t>
+          <t>699360-38-CM26</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -22312,12 +22312,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>60.505.000-k</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
@@ -22332,17 +22332,17 @@
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
@@ -22351,13 +22351,13 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>845.23</v>
+        <v>4587.2</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>1561-109-CM26</t>
+          <t>858-254-CM26</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -22382,12 +22382,12 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>61.504.000-2</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DEL CREDITO PRENDARIO</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -22397,28 +22397,32 @@
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K341" t="inlineStr"/>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>142889.96</v>
+        <v>4470.52</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>858-254-CM26</t>
+          <t>1561-109-CM26</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -22443,12 +22447,12 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.504.000-2</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>DIRECCION GENERAL DEL CREDITO PRENDARIO</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -22458,26 +22462,22 @@
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
-        </is>
-      </c>
-      <c r="K342" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr"/>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>4470.52</v>
+        <v>142889.96</v>
       </c>
     </row>
     <row r="343">
@@ -22613,7 +22613,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>836578-87-CM26</t>
+          <t>1533460-23-CM26</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -22638,12 +22638,12 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>61.101.045-1</t>
+          <t>65.261.347-0</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CORPORACIÓN MUNICIPAL DE CULTURA, DEPORTE Y DE FOMENTO DE DESARROLLO C</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -22653,12 +22653,12 @@
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
@@ -22672,13 +22672,13 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>1308.87</v>
+        <v>7130.93</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>1533460-23-CM26</t>
+          <t>836578-87-CM26</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -22703,12 +22703,12 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>65.261.347-0</t>
+          <t>61.101.045-1</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>CORPORACIÓN MUNICIPAL DE CULTURA, DEPORTE Y DE FOMENTO DE DESARROLLO C</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -22718,12 +22718,12 @@
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.334.381-2</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
@@ -22737,7 +22737,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>7130.93</v>
+        <v>1308.87</v>
       </c>
     </row>
     <row r="347">
@@ -23393,7 +23393,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2732-21-CM26</t>
+          <t>1750-263-CM26</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -23413,17 +23413,17 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>69.071.700-K</t>
+          <t>65.290.590-0</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
+          <t>DIRECCION NACIONAL DEL SERVICIO CIVIL</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -23452,13 +23452,13 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>165430.94</v>
+        <v>10644.31</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>1750-263-CM26</t>
+          <t>1606-281-CM26</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -23483,12 +23483,12 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>65.290.590-0</t>
+          <t>60.108.000-1</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>DIRECCION NACIONAL DEL SERVICIO CIVIL</t>
+          <t>AGENCIA CHILENA DE COOPERACION INTERNACIONAL PARA EL DESARROLLO</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -23498,12 +23498,12 @@
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K358" t="inlineStr">
@@ -23517,13 +23517,13 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>10644.31</v>
+        <v>6082.09</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>1606-281-CM26</t>
+          <t>2732-21-CM26</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -23543,17 +23543,17 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>60.108.000-1</t>
+          <t>69.071.700-K</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>AGENCIA CHILENA DE COOPERACION INTERNACIONAL PARA EL DESARROLLO</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -23563,12 +23563,12 @@
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K359" t="inlineStr">
@@ -23582,7 +23582,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>6082.09</v>
+        <v>165430.94</v>
       </c>
     </row>
     <row r="360">
@@ -23653,7 +23653,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2115-639-CM26</t>
+          <t>797305-49-CM26</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -23673,17 +23673,17 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>65.061.030-k</t>
+          <t>61.005.000-k</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>CENTRO DE REFERENCIA DE SALUD DE MAIPU</t>
+          <t>SUPERINTENDENCIA DE INSOLVENCIA Y REEMPRENDIMIENTO</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -23693,12 +23693,12 @@
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K361" t="inlineStr">
@@ -23712,13 +23712,13 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>72595.71000000001</v>
+        <v>76020.17999999999</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>797305-49-CM26</t>
+          <t>2115-639-CM26</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -23738,17 +23738,17 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>61.005.000-k</t>
+          <t>65.061.030-k</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE INSOLVENCIA Y REEMPRENDIMIENTO</t>
+          <t>CENTRO DE REFERENCIA DE SALUD DE MAIPU</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -23758,12 +23758,12 @@
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>92.580.000-7</t>
         </is>
       </c>
       <c r="K362" t="inlineStr">
@@ -23777,7 +23777,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>76020.17999999999</v>
+        <v>72595.71000000001</v>
       </c>
     </row>
     <row r="363">
@@ -23978,7 +23978,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>188-507-CM26</t>
+          <t>1271178-266-CM26</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -23998,17 +23998,17 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>70.933.700-9</t>
+          <t>71.369.900-4</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
+          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL DE MACUL</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -24018,28 +24018,32 @@
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
-        </is>
-      </c>
-      <c r="K366" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>34153</v>
+        <v>1479.16</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>1271178-266-CM26</t>
+          <t>1237849-145-CM26</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -24064,12 +24068,12 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>71.369.900-4</t>
+          <t>65.081.056-2</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL DE MACUL</t>
+          <t>CORPORACION MUNICIPAL DE FOMENTO AL DESARROLLO COMUNAL Y PRODUCTIVO DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -24079,17 +24083,17 @@
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K367" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
@@ -24098,13 +24102,13 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>1479.16</v>
+        <v>3077.1</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>1237849-145-CM26</t>
+          <t>188-507-CM26</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -24124,17 +24128,17 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>65.081.056-2</t>
+          <t>70.933.700-9</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE FOMENTO AL DESARROLLO COMUNAL Y PRODUCTIVO DE LA FLORIDA</t>
+          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
@@ -24144,26 +24148,22 @@
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K368" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.854.651-7</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr"/>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>3077.1</v>
+        <v>34153</v>
       </c>
     </row>
     <row r="369">
@@ -24299,7 +24299,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>1121-83-CM26</t>
+          <t>1393575-77-CM26</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -24324,12 +24324,12 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>61.706.000-0</t>
+          <t>65.010.882-5</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>Comisión Chilena del Cobre - COCHILCO</t>
+          <t>FUNDACION IMAGEN DE CHILE</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -24339,12 +24339,12 @@
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K371" t="inlineStr">
@@ -24358,13 +24358,13 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>30913.52</v>
+        <v>1422.05</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>1121-84-CM26</t>
+          <t>1287766-76-CM26</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -24384,17 +24384,17 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>61.706.000-0</t>
+          <t>65.199.980-4</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>Comisión Chilena del Cobre - COCHILCO</t>
+          <t>Corporación Municipal de Deportes de Ñuñoa</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -24404,12 +24404,12 @@
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K372" t="inlineStr">
@@ -24423,13 +24423,13 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>7909.38</v>
+        <v>4080.32</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>1393575-77-CM26</t>
+          <t>1121-84-CM26</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -24454,12 +24454,12 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>65.010.882-5</t>
+          <t>61.706.000-0</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>FUNDACION IMAGEN DE CHILE</t>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -24469,12 +24469,12 @@
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K373" t="inlineStr">
@@ -24488,13 +24488,13 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>1422.05</v>
+        <v>7909.38</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>1287766-76-CM26</t>
+          <t>1121-83-CM26</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -24514,17 +24514,17 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>65.199.980-4</t>
+          <t>61.706.000-0</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Deportes de Ñuñoa</t>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -24534,12 +24534,12 @@
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K374" t="inlineStr">
@@ -24553,7 +24553,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>4080.32</v>
+        <v>30913.52</v>
       </c>
     </row>
     <row r="375">
@@ -25014,7 +25014,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>188-517-CM26</t>
+          <t>1260-126-SE26</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -25034,17 +25034,17 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>70.933.700-9</t>
+          <t>61.923.200-3</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -25054,17 +25054,17 @@
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>880443249</t>
         </is>
       </c>
       <c r="K382" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Extranjero</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">
@@ -25073,13 +25073,13 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>5810.39</v>
+        <v>106407.42</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>1147293-240-CM26</t>
+          <t>188-517-CM26</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -25104,12 +25104,12 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>70.930.000-8</t>
+          <t>70.933.700-9</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Fundación para la Innovación Agraria</t>
+          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -25119,12 +25119,12 @@
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K383" t="inlineStr">
@@ -25138,13 +25138,13 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>17915.39</v>
+        <v>5810.39</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>1260-126-SE26</t>
+          <t>1147293-240-CM26</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -25164,17 +25164,17 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>61.923.200-3</t>
+          <t>70.930.000-8</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>Fundación para la Innovación Agraria</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -25184,17 +25184,17 @@
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>880443249</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K384" t="inlineStr">
         <is>
-          <t>Extranjero</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L384" t="inlineStr">
@@ -25203,7 +25203,7 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>106407.42</v>
+        <v>17915.39</v>
       </c>
     </row>
     <row r="385">
@@ -25794,7 +25794,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>979-1248-CM26</t>
+          <t>2981-1144-CM26</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -25814,17 +25814,17 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
@@ -25853,13 +25853,13 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>28709.51</v>
+        <v>5772.69</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2434-37-CM26</t>
+          <t>979-1248-CM26</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -25884,12 +25884,12 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>69.254.300-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -25899,12 +25899,12 @@
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K395" t="inlineStr">
@@ -25918,13 +25918,13 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>120303.05</v>
+        <v>28709.51</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>2981-1144-CM26</t>
+          <t>2434-37-CM26</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -25944,17 +25944,17 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>69.254.300-9</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -25964,12 +25964,12 @@
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K396" t="inlineStr">
@@ -25983,7 +25983,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>5772.69</v>
+        <v>120303.05</v>
       </c>
     </row>
     <row r="397">
@@ -26119,7 +26119,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>3363-94-CM26</t>
+          <t>1533460-50-CM26</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -26144,12 +26144,12 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>61.101.045-1</t>
+          <t>65.261.347-0</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CORPORACIÓN MUNICIPAL DE CULTURA, DEPORTE Y DE FOMENTO DE DESARROLLO C</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
@@ -26159,12 +26159,12 @@
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K399" t="inlineStr">
@@ -26178,13 +26178,13 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>2498.75</v>
+        <v>3961.63</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>1533460-50-CM26</t>
+          <t>3363-94-CM26</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -26204,17 +26204,17 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>65.261.347-0</t>
+          <t>61.101.045-1</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>CORPORACIÓN MUNICIPAL DE CULTURA, DEPORTE Y DE FOMENTO DE DESARROLLO C</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
@@ -26224,12 +26224,12 @@
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.334.381-2</t>
         </is>
       </c>
       <c r="K400" t="inlineStr">
@@ -26243,13 +26243,13 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>3961.63</v>
+        <v>2498.75</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>1385462-180-CM26</t>
+          <t>2341-499-CM26</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -26274,12 +26274,12 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>69.072.700-5</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
@@ -26289,32 +26289,28 @@
       </c>
       <c r="I401" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K401" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.854.651-7</t>
+        </is>
+      </c>
+      <c r="K401" t="inlineStr"/>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>6039.25</v>
+        <v>34986</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>2341-499-CM26</t>
+          <t>1385462-180-CM26</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -26334,17 +26330,17 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>69.072.700-5</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
@@ -26354,22 +26350,26 @@
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
-        </is>
-      </c>
-      <c r="K402" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>34986</v>
+        <v>6039.25</v>
       </c>
     </row>
     <row r="403">
@@ -26460,7 +26460,7 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
@@ -26525,7 +26525,7 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
@@ -26635,66 +26635,972 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
+          <t>812261-1397-CM26</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>65.075.485-9</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>MSLI Latam Inc.</t>
+        </is>
+      </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K407" t="inlineStr"/>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M407" s="2" t="n">
+        <v>223910.4</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
           <t>598-250-SE26</t>
         </is>
       </c>
-      <c r="B407" t="inlineStr">
-        <is>
-          <t>2239-11-LR24</t>
-        </is>
-      </c>
-      <c r="C407" t="inlineStr">
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
         <is>
           <t>sep-2026</t>
         </is>
       </c>
-      <c r="D407" t="inlineStr">
+      <c r="D408" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="E407" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F407" t="inlineStr">
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
         <is>
           <t>61.513.000-1</t>
         </is>
       </c>
-      <c r="G407" t="inlineStr">
+      <c r="G408" t="inlineStr">
         <is>
           <t>DIRECCION PREVISION DE CARABINEROS DE CHILE</t>
         </is>
       </c>
-      <c r="H407" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I407" t="inlineStr">
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
         <is>
           <t>Seidor Chile S.A.</t>
         </is>
       </c>
-      <c r="J407" t="inlineStr">
+      <c r="J408" t="inlineStr">
         <is>
           <t>96.986.170-4</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L407" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M407" s="2" t="n">
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M408" s="2" t="n">
         <v>340177.13</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>743848-35-CM26</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>61.980.250-0</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>SEGUNDO TRIBUNAL AMBIENTAL</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>Netsus SpA</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>76.288.338-4</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M409" s="2" t="n">
+        <v>19038.1</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>857-148-CM26</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>72.576.700-5</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE LA DISCAPACIDAD</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M410" s="2" t="n">
+        <v>19335.95</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2287-784-CM26</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>69.253.700-9</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE MACUL</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M411" s="2" t="n">
+        <v>23436.34</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>1301883-261-CM26</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>Intercity S.A.</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M412" s="2" t="n">
+        <v>2751.09</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>1029940-84-CM26</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>62.000.370-0</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL PATRIMONIO CULTURAL</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>Netsus SpA</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>76.288.338-4</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M413" s="2" t="n">
+        <v>12772.39</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>1561-180-CM26</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>61.504.000-2</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DEL CREDITO PRENDARIO</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>Intercity S.A.</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M414" s="2" t="n">
+        <v>8597.16</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>539119-3323-CM26</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>60.505.720-9</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M415" s="2" t="n">
+        <v>1171.82</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>628-114-CM26</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>60.107.000-6</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M416" s="2" t="n">
+        <v>94562.16</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>1020-334-CM26</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M417" s="2" t="n">
+        <v>1692.41</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2153-631-CM26</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>61.608.503-4</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>Hospital Sanatorio San José de Maipo</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M418" s="2" t="n">
+        <v>15655.64</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>1230771-41-CM26</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>65.080.277-2</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>Corporación de Desarrollo Social de la Municipalidad de Independencia</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M419" s="2" t="n">
+        <v>1774.05</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>4931-123-CM26</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>65.613.130-6</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>COMISION ADMINISTRADORA DEL SISTEMA DE CREDITOS P. ESTUDIOS SUPERIORES</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>Intercity S.A.</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M420" s="2" t="n">
+        <v>1719.43</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2982-90-CM26</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>60.506.000-5</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M421" s="2" t="n">
+        <v>7481.38</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/metropolitana.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/metropolitana.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M421"/>
+  <dimension ref="A1:M422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1611,7 +1611,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2673-44-CM25</t>
+          <t>5768-38-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.072.900-8</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1651,12 +1651,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1670,13 +1670,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>99781.5</v>
+        <v>27555.64</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5768-38-CM25</t>
+          <t>2673-44-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1696,17 +1696,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.072.900-8</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1716,12 +1716,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1735,13 +1735,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>27555.64</v>
+        <v>99781.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4928-23-CM25</t>
+          <t>858-98-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>92.580.000-7</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1800,13 +1800,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>64891.78</v>
+        <v>10757.12</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>858-98-CM25</t>
+          <t>4928-23-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1846,17 +1846,17 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1865,7 +1865,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>10757.12</v>
+        <v>64891.78</v>
       </c>
     </row>
     <row r="23">
@@ -3350,7 +3350,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4928-38-CM25</t>
+          <t>4928-33-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3409,13 +3409,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>5076.25</v>
+        <v>6133.81</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4928-33-CM25</t>
+          <t>4928-38-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3474,7 +3474,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>6133.81</v>
+        <v>5076.25</v>
       </c>
     </row>
     <row r="48">
@@ -3610,7 +3610,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4099-266-CM25</t>
+          <t>514862-477-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3635,12 +3635,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.073.300-5</t>
+          <t>71.234.100-9</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIA PINTO</t>
+          <t>CORPORACION MUNICIPAL DE PENALOLEN PARA EL DESARROLO SOCIAL CORMUP</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3669,13 +3669,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>4230.21</v>
+        <v>15017.25</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>514862-477-CM25</t>
+          <t>4099-266-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>71.234.100-9</t>
+          <t>69.073.300-5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE PENALOLEN PARA EL DESARROLO SOCIAL CORMUP</t>
+          <t>I MUNICIPALIDAD DE MARIA PINTO</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3734,7 +3734,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>15017.25</v>
+        <v>4230.21</v>
       </c>
     </row>
     <row r="52">
@@ -4455,7 +4455,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>798018-37-CM25</t>
+          <t>1057499-258-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>65.073.222-7</t>
+          <t>61.608.108-K</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4495,32 +4495,28 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>4356.66</v>
+        <v>151139.52</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1057473-261-CM25</t>
+          <t>798018-37-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4545,12 +4541,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.999.030-7</t>
+          <t>65.073.222-7</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Centro Metropolitano de Atención Prehospitalaria</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4560,12 +4556,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4579,13 +4575,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>70821.66</v>
+        <v>4356.66</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1057499-258-CM25</t>
+          <t>1057473-261-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4610,12 +4606,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.608.108-K</t>
+          <t>61.999.030-7</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
+          <t>Centro Metropolitano de Atención Prehospitalaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4625,22 +4621,26 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>151139.52</v>
+        <v>70821.66</v>
       </c>
     </row>
     <row r="66">
@@ -6316,7 +6316,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1232911-50-CM25</t>
+          <t>1375761-49-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>65.115.629-7</t>
+          <t>61.981.330-8</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Deportes de Colina</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6375,13 +6375,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>7812.11</v>
+        <v>13423.2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1375761-49-CM25</t>
+          <t>1232911-50-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6406,12 +6406,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.981.330-8</t>
+          <t>65.115.629-7</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
+          <t>Corporación Municipal de Deportes de Colina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6421,12 +6421,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6440,13 +6440,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>13423.2</v>
+        <v>7812.11</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>3328-2176-CM25</t>
+          <t>4928-63-CM25</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6486,12 +6486,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6505,7 +6505,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>1201.16</v>
+        <v>14805.74</v>
       </c>
     </row>
     <row r="95">
@@ -6576,7 +6576,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>4928-63-CM25</t>
+          <t>3328-2176-CM25</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6601,12 +6601,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6616,12 +6616,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -6635,7 +6635,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>14805.74</v>
+        <v>1201.16</v>
       </c>
     </row>
     <row r="97">
@@ -6763,7 +6763,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1447790-6-CM25</t>
+          <t>1447792-9-CM25</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6822,13 +6822,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>9131.01</v>
+        <v>13696.52</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1447792-9-CM25</t>
+          <t>1447790-6-CM25</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6887,7 +6887,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>13696.52</v>
+        <v>9131.01</v>
       </c>
     </row>
     <row r="101">
@@ -8311,7 +8311,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>622-543-CM25</t>
+          <t>797305-87-CM25</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>60.805.000-0</t>
+          <t>61.005.000-k</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
+          <t>SUPERINTENDENCIA DE INSOLVENCIA Y REEMPRENDIMIENTO</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -8370,13 +8370,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>26892.81</v>
+        <v>75963.64999999999</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>797305-87-CM25</t>
+          <t>622-543-CM25</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8401,12 +8401,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>61.005.000-k</t>
+          <t>60.805.000-0</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE INSOLVENCIA Y REEMPRENDIMIENTO</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8416,12 +8416,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>92.580.000-7</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -8435,7 +8435,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>75963.64999999999</v>
+        <v>26892.81</v>
       </c>
     </row>
     <row r="125">
@@ -8758,7 +8758,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1271178-319-CM25</t>
+          <t>1375746-55-CM25</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>71.369.900-4</t>
+          <t>61.981.280-8</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL DE MACUL</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ACONCAGUA</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8798,12 +8798,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -8817,13 +8817,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>1281.63</v>
+        <v>13907.53</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1375746-55-CM25</t>
+          <t>1271178-319-CM25</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8848,12 +8848,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>61.981.280-8</t>
+          <t>71.369.900-4</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ACONCAGUA</t>
+          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL DE MACUL</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8863,12 +8863,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.334.381-2</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -8882,7 +8882,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>13907.53</v>
+        <v>1281.63</v>
       </c>
     </row>
     <row r="132">
@@ -9270,7 +9270,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1607-191-CM25</t>
+          <t>1076403-37-CM25</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9295,12 +9295,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>60.601.000-1</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
+          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -9310,12 +9310,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.553.790-6</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -9329,7 +9329,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>53878.44</v>
+        <v>891357.6</v>
       </c>
     </row>
     <row r="139">
@@ -9400,7 +9400,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1076403-37-CM25</t>
+          <t>1607-191-CM25</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9425,12 +9425,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>60.601.000-1</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
+          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -9440,12 +9440,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -9459,7 +9459,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>891357.6</v>
+        <v>53878.44</v>
       </c>
     </row>
     <row r="141">
@@ -9725,7 +9725,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>628-339-CM25</t>
+          <t>623663-460-CM25</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9745,17 +9745,17 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>60.107.000-6</t>
+          <t>65.030.848-4</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
+          <t>AGENCIA CHILENA DE EFICIENCIA ENERGETICA</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -9784,13 +9784,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>82419.39999999999</v>
+        <v>36945.22</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>623663-460-CM25</t>
+          <t>628-339-CM25</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9810,17 +9810,17 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>65.030.848-4</t>
+          <t>60.107.000-6</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>AGENCIA CHILENA DE EFICIENCIA ENERGETICA</t>
+          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -9849,7 +9849,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>36945.22</v>
+        <v>82419.39999999999</v>
       </c>
     </row>
     <row r="147">
@@ -10176,7 +10176,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>608897-11250-CM25</t>
+          <t>1057501-24877-CM25</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -10196,17 +10196,17 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>61.979.930-5</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -10216,32 +10216,28 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>9727.92</v>
+        <v>67173.12</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1019-548-CM25</t>
+          <t>1019-549-CM25</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -10281,32 +10277,28 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>4863.77</v>
+        <v>73666.52</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1019-549-CM25</t>
+          <t>1019-548-CM25</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -10346,28 +10338,32 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>73666.52</v>
+        <v>4863.77</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1057501-24877-CM25</t>
+          <t>608897-11250-CM25</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -10387,17 +10383,17 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.979.930-5</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -10407,22 +10403,26 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K155" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>67173.12</v>
+        <v>9727.92</v>
       </c>
     </row>
     <row r="156">
@@ -10554,7 +10554,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>979-2016-CM25</t>
+          <t>5520-10754-CM25</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10574,17 +10574,17 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10594,12 +10594,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>77.553.790-6</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -10613,13 +10613,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>52865.75</v>
+        <v>5733.42</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>5520-10754-CM25</t>
+          <t>979-2016-CM25</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10639,17 +10639,17 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10659,12 +10659,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -10678,7 +10678,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>5733.42</v>
+        <v>52865.75</v>
       </c>
     </row>
     <row r="160">
@@ -12618,7 +12618,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>14-654-CM25</t>
+          <t>1260-277-CM25</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12643,12 +12643,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>61.923.200-3</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12658,12 +12658,12 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -12677,13 +12677,13 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>22357.24</v>
+        <v>30398.55</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1260-276-CM25</t>
+          <t>14-654-CM25</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12708,12 +12708,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>61.923.200-3</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12723,12 +12723,12 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -12742,13 +12742,13 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>19852.06</v>
+        <v>22357.24</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1260-277-CM25</t>
+          <t>937232-1136-CM25</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12773,12 +12773,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>61.923.200-3</t>
+          <t>61.980.620-4</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>CENTRO DE REFERENCIA DE SALUD HOSPITAL PROVINCIA CORDILLERA</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -12807,13 +12807,13 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>30398.55</v>
+        <v>92320.2</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>937232-1136-CM25</t>
+          <t>1260-276-CM25</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12838,12 +12838,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>61.980.620-4</t>
+          <t>61.923.200-3</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>CENTRO DE REFERENCIA DE SALUD HOSPITAL PROVINCIA CORDILLERA</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12853,12 +12853,12 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.334.381-2</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -12872,7 +12872,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>92320.2</v>
+        <v>19852.06</v>
       </c>
     </row>
     <row r="194">
@@ -13203,7 +13203,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1057468-288-CM25</t>
+          <t>1121-150-CM25</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -13228,12 +13228,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>61.608.600-6</t>
+          <t>61.706.000-0</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO CENTRAL</t>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -13243,12 +13243,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -13262,13 +13262,13 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>13321.42</v>
+        <v>3611.55</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1121-150-CM25</t>
+          <t>1057468-288-CM25</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -13293,12 +13293,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>61.706.000-0</t>
+          <t>61.608.600-6</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Comisión Chilena del Cobre - COCHILCO</t>
+          <t>SERVICIO DE SALUD METROPOLITANO CENTRAL</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -13308,12 +13308,12 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -13327,7 +13327,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>3611.55</v>
+        <v>13321.42</v>
       </c>
     </row>
     <row r="201">
@@ -16311,7 +16311,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1415862-13-CM26</t>
+          <t>1415862-12-CM26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -16370,13 +16370,13 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>70962.08</v>
+        <v>69234.8</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1372962-3-CM26</t>
+          <t>1415862-13-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -16396,17 +16396,17 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>65.143.474-2</t>
+          <t>61.533.000-0</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>FUNDACION PARA LA REHABILITACIÓN DE PERSONAS CON DISCAPACIDAD DE LA COMUNA DE SAN PEDRO DE ATACAMA</t>
+          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -16435,13 +16435,13 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>1651.17</v>
+        <v>70962.08</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>1415862-12-CM26</t>
+          <t>1372962-3-CM26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -16461,17 +16461,17 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>61.533.000-0</t>
+          <t>65.143.474-2</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
+          <t>FUNDACION PARA LA REHABILITACIÓN DE PERSONAS CON DISCAPACIDAD DE LA COMUNA DE SAN PEDRO DE ATACAMA</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -16500,7 +16500,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>69234.8</v>
+        <v>1651.17</v>
       </c>
     </row>
     <row r="250">
@@ -17083,7 +17083,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>1386073-60-CM26</t>
+          <t>1388961-131-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -17103,17 +17103,17 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>71.004.200-4</t>
+          <t>65.118.035-K</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>CORP CULTURAL DE LAS CONDES</t>
+          <t>ASOCIACION DE MUNICIPALIDADES PARA LA SEGURIDAD CIUDADANA EN LA ZONA ORIENTE</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -17123,32 +17123,28 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>SUPER SOFTWARE SPA</t>
+          <t>ASESORIAS EN INFORMATICA ZONA-TI LIMITADA</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>76.486.150-7</t>
-        </is>
-      </c>
-      <c r="K259" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.338.883-2</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr"/>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>15244.28</v>
+        <v>6417.17</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>1388961-131-CM26</t>
+          <t>1386073-60-CM26</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -17173,12 +17169,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>65.118.035-K</t>
+          <t>71.004.200-4</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>ASOCIACION DE MUNICIPALIDADES PARA LA SEGURIDAD CIUDADANA EN LA ZONA ORIENTE</t>
+          <t>CORP CULTURAL DE LAS CONDES</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -17188,22 +17184,26 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>ASESORIAS EN INFORMATICA ZONA-TI LIMITADA</t>
+          <t>SUPER SOFTWARE SPA</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>76.338.883-2</t>
-        </is>
-      </c>
-      <c r="K260" t="inlineStr"/>
+          <t>76.486.150-7</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>6417.17</v>
+        <v>15244.28</v>
       </c>
     </row>
     <row r="261">
@@ -17664,7 +17664,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>975-102-CM26</t>
+          <t>975-101-CM26</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -17704,28 +17704,32 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>79.770.640-k</t>
-        </is>
-      </c>
-      <c r="K268" t="inlineStr"/>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>4470.83</v>
+        <v>224533.9</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>975-101-CM26</t>
+          <t>975-102-CM26</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -17765,26 +17769,22 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
-        </is>
-      </c>
-      <c r="K269" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.770.640-k</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr"/>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>224533.9</v>
+        <v>4470.83</v>
       </c>
     </row>
     <row r="270">
@@ -18046,7 +18046,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>1415862-20-CM26</t>
+          <t>1057473-140-CM26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -18071,12 +18071,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>61.533.000-0</t>
+          <t>61.999.030-7</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
+          <t>Centro Metropolitano de Atención Prehospitalaria</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -18086,12 +18086,12 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
@@ -18105,13 +18105,13 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>216159.22</v>
+        <v>70764.53999999999</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>1057473-140-CM26</t>
+          <t>1415862-20-CM26</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -18131,17 +18131,17 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>61.999.030-7</t>
+          <t>61.533.000-0</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Centro Metropolitano de Atención Prehospitalaria</t>
+          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -18151,12 +18151,12 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
@@ -18170,7 +18170,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>70764.53999999999</v>
+        <v>216159.22</v>
       </c>
     </row>
     <row r="276">
@@ -18261,7 +18261,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -19529,7 +19529,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>14-185-CM26</t>
+          <t>577290-45-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>61.979.750-7</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -19569,26 +19569,22 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
-        </is>
-      </c>
-      <c r="K297" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.770.640-k</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr"/>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>3846.89</v>
+        <v>2579.33</v>
       </c>
     </row>
     <row r="298">
@@ -19789,7 +19785,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>577290-45-CM26</t>
+          <t>14-185-CM26</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -19814,12 +19810,12 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>61.979.750-7</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TRANSPORTES</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -19829,22 +19825,26 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>79.770.640-k</t>
-        </is>
-      </c>
-      <c r="K301" t="inlineStr"/>
+          <t>76.083.145-k</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>2579.33</v>
+        <v>3846.89</v>
       </c>
     </row>
     <row r="302">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
@@ -21280,7 +21280,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
@@ -21345,7 +21345,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
@@ -21516,7 +21516,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>5768-102-CM26</t>
+          <t>1368-34-CM26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -21536,17 +21536,17 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>75.980.060-5</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -21556,12 +21556,12 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
@@ -21575,7 +21575,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>54978</v>
+        <v>10769.86</v>
       </c>
     </row>
     <row r="329">
@@ -21772,7 +21772,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>1368-34-CM26</t>
+          <t>5768-102-CM26</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -21792,17 +21792,17 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>75.980.060-5</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -21812,12 +21812,12 @@
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
@@ -21831,7 +21831,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>10769.86</v>
+        <v>54978</v>
       </c>
     </row>
     <row r="333">
@@ -21987,7 +21987,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
@@ -22292,7 +22292,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>699360-38-CM26</t>
+          <t>1561-110-CM26</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -22317,12 +22317,12 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>60.505.000-k</t>
+          <t>61.504.000-2</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION GENERAL DEL CREDITO PRENDARIO</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -22332,32 +22332,28 @@
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K340" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr"/>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>4587.2</v>
+        <v>11195.52</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>858-254-CM26</t>
+          <t>699360-38-CM26</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -22372,22 +22368,22 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>60.505.000-k</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -22397,12 +22393,12 @@
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
@@ -22416,13 +22412,13 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>4470.52</v>
+        <v>4587.2</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>1561-109-CM26</t>
+          <t>858-254-CM26</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -22447,12 +22443,12 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>61.504.000-2</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DEL CREDITO PRENDARIO</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -22462,28 +22458,32 @@
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K342" t="inlineStr"/>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>142889.96</v>
+        <v>4470.52</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>2582-255-SE26</t>
+          <t>1561-109-CM26</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -22498,7 +22498,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -22508,12 +22508,12 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>69.070.100-6</t>
+          <t>61.504.000-2</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTIAGO</t>
+          <t>DIRECCION GENERAL DEL CREDITO PRENDARIO</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -22523,32 +22523,28 @@
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K343" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr"/>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>218562.54</v>
+        <v>142889.96</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>3420-34-CM26</t>
+          <t>2582-255-SE26</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -22563,7 +22559,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -22573,12 +22569,12 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>61.101.054-0</t>
+          <t>69.070.100-6</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE SANTIAGO</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -22588,17 +22584,17 @@
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
@@ -22607,13 +22603,13 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>1901.77</v>
+        <v>218562.54</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>1533460-23-CM26</t>
+          <t>3420-34-CM26</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -22628,7 +22624,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -22638,12 +22634,12 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>65.261.347-0</t>
+          <t>61.101.054-0</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>CORPORACIÓN MUNICIPAL DE CULTURA, DEPORTE Y DE FOMENTO DE DESARROLLO C</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -22653,17 +22649,17 @@
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
@@ -22672,13 +22668,13 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>7130.93</v>
+        <v>1901.77</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>836578-87-CM26</t>
+          <t>1533460-23-CM26</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -22703,12 +22699,12 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>61.101.045-1</t>
+          <t>65.261.347-0</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CORPORACIÓN MUNICIPAL DE CULTURA, DEPORTE Y DE FOMENTO DE DESARROLLO C</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -22718,12 +22714,12 @@
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
@@ -22737,13 +22733,13 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>1308.87</v>
+        <v>7130.93</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2412-433-CM26</t>
+          <t>836578-87-CM26</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -22758,7 +22754,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -22768,12 +22764,12 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>69.254.100-6</t>
+          <t>61.101.045-1</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LO PRADO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -22783,17 +22779,17 @@
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.334.381-2</t>
         </is>
       </c>
       <c r="K347" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
@@ -22802,13 +22798,13 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>2324.39</v>
+        <v>1308.87</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>1068038-18-CM26</t>
+          <t>2412-433-CM26</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -22823,22 +22819,22 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>60.511.000-2</t>
+          <t>69.254.100-6</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL INTERIOR</t>
+          <t>I MUNICIPALIDAD DE LO PRADO</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -22848,17 +22844,17 @@
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K348" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
@@ -22867,13 +22863,13 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>1664.43</v>
+        <v>2324.39</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2483-477-CM26</t>
+          <t>1068038-18-CM26</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -22893,17 +22889,17 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>69.071.300-4</t>
+          <t>60.511.000-2</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILICURA</t>
+          <t>SUBSECRETARIA DEL INTERIOR</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -22913,12 +22909,12 @@
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K349" t="inlineStr">
@@ -22932,13 +22928,13 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>175629.72</v>
+        <v>1664.43</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>2343-337-CM26</t>
+          <t>2483-477-CM26</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -22953,22 +22949,22 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>69.070.100-6</t>
+          <t>69.071.300-4</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTIAGO</t>
+          <t>I MUNICIPALIDAD DE QUILICURA</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -22978,17 +22974,17 @@
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
@@ -22997,13 +22993,13 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>4226.17</v>
+        <v>175629.72</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>1457282-36-CM26</t>
+          <t>2343-337-CM26</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -23018,22 +23014,22 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>65.011.263-6</t>
+          <t>69.070.100-6</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>CORPORACION CENTRO CULTURAL GABRIELA MISTRAL</t>
+          <t>I MUNICIPALIDAD DE SANTIAGO</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -23043,17 +23039,17 @@
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K351" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
@@ -23062,13 +23058,13 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>18933.61</v>
+        <v>4226.17</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>3420-37-CM26</t>
+          <t>1457282-36-CM26</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -23083,22 +23079,22 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>61.101.054-0</t>
+          <t>65.011.263-6</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CORPORACION CENTRO CULTURAL GABRIELA MISTRAL</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -23108,17 +23104,17 @@
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K352" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L352" t="inlineStr">
@@ -23127,13 +23123,13 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>21976.06</v>
+        <v>18933.61</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>1602-80-CM26</t>
+          <t>3420-37-CM26</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -23148,22 +23144,22 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>61.101.054-0</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -23173,17 +23169,17 @@
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K353" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L353" t="inlineStr">
@@ -23192,13 +23188,13 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>47204.92</v>
+        <v>21976.06</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>585-94-CM26</t>
+          <t>1602-80-CM26</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -23213,7 +23209,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -23223,12 +23219,12 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -23238,17 +23234,17 @@
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K354" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L354" t="inlineStr">
@@ -23257,13 +23253,13 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>326243.38</v>
+        <v>47204.92</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>514862-462-CM26</t>
+          <t>585-94-CM26</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -23288,12 +23284,12 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>71.234.100-9</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE PENALOLEN PARA EL DESARROLO SOCIAL CORMUP</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -23303,12 +23299,12 @@
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K355" t="inlineStr">
@@ -23322,13 +23318,13 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>21360.5</v>
+        <v>326243.38</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>858-299-CM26</t>
+          <t>514862-462-CM26</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -23338,27 +23334,27 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>71.234.100-9</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>CORPORACION MUNICIPAL DE PENALOLEN PARA EL DESARROLO SOCIAL CORMUP</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -23368,12 +23364,12 @@
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K356" t="inlineStr">
@@ -23387,13 +23383,13 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>24072.03</v>
+        <v>21360.5</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>1750-263-CM26</t>
+          <t>858-299-CM26</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -23408,7 +23404,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -23418,12 +23414,12 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>65.290.590-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>DIRECCION NACIONAL DEL SERVICIO CIVIL</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -23433,12 +23429,12 @@
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K357" t="inlineStr">
@@ -23452,7 +23448,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>10644.31</v>
+        <v>24072.03</v>
       </c>
     </row>
     <row r="358">
@@ -23523,7 +23519,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2732-21-CM26</t>
+          <t>1750-263-CM26</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -23543,17 +23539,17 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>69.071.700-K</t>
+          <t>65.290.590-0</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
+          <t>DIRECCION NACIONAL DEL SERVICIO CIVIL</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -23582,13 +23578,13 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>165430.94</v>
+        <v>10644.31</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>539119-2520-CM26</t>
+          <t>2732-21-CM26</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -23603,22 +23599,22 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>69.071.700-K</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -23628,17 +23624,17 @@
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K360" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L360" t="inlineStr">
@@ -23647,13 +23643,13 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>845.23</v>
+        <v>165430.94</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>797305-49-CM26</t>
+          <t>539119-2520-CM26</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -23668,7 +23664,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -23678,12 +23674,12 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>61.005.000-k</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE INSOLVENCIA Y REEMPRENDIMIENTO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -23693,17 +23689,17 @@
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K361" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
@@ -23712,13 +23708,13 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>76020.17999999999</v>
+        <v>845.23</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2115-639-CM26</t>
+          <t>797305-49-CM26</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -23738,17 +23734,17 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>65.061.030-k</t>
+          <t>61.005.000-k</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>CENTRO DE REFERENCIA DE SALUD DE MAIPU</t>
+          <t>SUPERINTENDENCIA DE INSOLVENCIA Y REEMPRENDIMIENTO</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -23758,12 +23754,12 @@
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K362" t="inlineStr">
@@ -23777,13 +23773,13 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>72595.71000000001</v>
+        <v>76020.17999999999</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>3894-65-CM26</t>
+          <t>2115-639-CM26</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -23798,7 +23794,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -23808,12 +23804,12 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>69.071.400-0</t>
+          <t>65.061.030-k</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAMPA</t>
+          <t>CENTRO DE REFERENCIA DE SALUD DE MAIPU</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -23823,12 +23819,12 @@
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>92.580.000-7</t>
         </is>
       </c>
       <c r="K363" t="inlineStr">
@@ -23842,7 +23838,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>64867.5</v>
+        <v>72595.71000000001</v>
       </c>
     </row>
     <row r="364">
@@ -23913,7 +23909,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>604944-82-CM26</t>
+          <t>3894-65-CM26</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -23933,17 +23929,17 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>61.979.870-8</t>
+          <t>69.071.400-0</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DEFENSA</t>
+          <t>I MUNICIPALIDAD DE LAMPA</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -23953,12 +23949,12 @@
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K365" t="inlineStr">
@@ -23972,13 +23968,13 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>11132.26</v>
+        <v>64867.5</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>1271178-266-CM26</t>
+          <t>604944-82-CM26</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -23993,7 +23989,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -24003,12 +23999,12 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>71.369.900-4</t>
+          <t>61.979.870-8</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL DE MACUL</t>
+          <t>SUBSECRETARIA DE DEFENSA</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -24018,17 +24014,17 @@
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
@@ -24037,13 +24033,13 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>1479.16</v>
+        <v>11132.26</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>1237849-145-CM26</t>
+          <t>1271178-266-CM26</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -24068,12 +24064,12 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>65.081.056-2</t>
+          <t>71.369.900-4</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE FOMENTO AL DESARROLLO COMUNAL Y PRODUCTIVO DE LA FLORIDA</t>
+          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL DE MACUL</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -24083,17 +24079,17 @@
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K367" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
@@ -24102,13 +24098,13 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>3077.1</v>
+        <v>1479.16</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>188-507-CM26</t>
+          <t>1237849-145-CM26</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -24128,17 +24124,17 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>70.933.700-9</t>
+          <t>65.081.056-2</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
+          <t>CORPORACION MUNICIPAL DE FOMENTO AL DESARROLLO COMUNAL Y PRODUCTIVO DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
@@ -24148,28 +24144,32 @@
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
-        </is>
-      </c>
-      <c r="K368" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>34153</v>
+        <v>3077.1</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>1750-284-CM26</t>
+          <t>188-507-CM26</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -24184,22 +24184,22 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>65.290.590-0</t>
+          <t>70.933.700-9</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>DIRECCION NACIONAL DEL SERVICIO CIVIL</t>
+          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -24209,32 +24209,28 @@
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K369" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.854.651-7</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr"/>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>46156.53</v>
+        <v>34153</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>937232-578-CM26</t>
+          <t>1750-284-CM26</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -24249,22 +24245,22 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>61.980.620-4</t>
+          <t>65.290.590-0</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>CENTRO DE REFERENCIA DE SALUD HOSPITAL PROVINCIA CORDILLERA</t>
+          <t>DIRECCION NACIONAL DEL SERVICIO CIVIL</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -24274,12 +24270,12 @@
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K370" t="inlineStr">
@@ -24293,13 +24289,13 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>2112.87</v>
+        <v>46156.53</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>1393575-77-CM26</t>
+          <t>937232-578-CM26</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -24314,22 +24310,22 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>65.010.882-5</t>
+          <t>61.980.620-4</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>FUNDACION IMAGEN DE CHILE</t>
+          <t>CENTRO DE REFERENCIA DE SALUD HOSPITAL PROVINCIA CORDILLERA</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -24339,12 +24335,12 @@
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K371" t="inlineStr">
@@ -24358,13 +24354,13 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>1422.05</v>
+        <v>2112.87</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>1287766-76-CM26</t>
+          <t>1121-83-CM26</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -24384,17 +24380,17 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>65.199.980-4</t>
+          <t>61.706.000-0</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Deportes de Ñuñoa</t>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -24404,12 +24400,12 @@
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K372" t="inlineStr">
@@ -24423,7 +24419,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>4080.32</v>
+        <v>30913.52</v>
       </c>
     </row>
     <row r="373">
@@ -24494,7 +24490,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>1121-83-CM26</t>
+          <t>1393575-77-CM26</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -24519,12 +24515,12 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>61.706.000-0</t>
+          <t>65.010.882-5</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Comisión Chilena del Cobre - COCHILCO</t>
+          <t>FUNDACION IMAGEN DE CHILE</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -24534,12 +24530,12 @@
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K374" t="inlineStr">
@@ -24553,13 +24549,13 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>30913.52</v>
+        <v>1422.05</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>857-121-CM26</t>
+          <t>1287766-76-CM26</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -24574,7 +24570,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -24584,12 +24580,12 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>72.576.700-5</t>
+          <t>65.199.980-4</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE LA DISCAPACIDAD</t>
+          <t>Corporación Municipal de Deportes de Ñuñoa</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -24618,13 +24614,13 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>50772.18</v>
+        <v>4080.32</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>4246-85-CM26</t>
+          <t>857-121-CM26</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -24639,22 +24635,22 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>61.976.100-6</t>
+          <t>72.576.700-5</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE CASINOS DE JUEGO</t>
+          <t>SERVICIO NACIONAL DE LA DISCAPACIDAD</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -24664,12 +24660,12 @@
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K376" t="inlineStr">
@@ -24683,13 +24679,13 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>21128.69</v>
+        <v>50772.18</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>1375746-102-CM26</t>
+          <t>4246-85-CM26</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -24714,12 +24710,12 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>61.981.280-8</t>
+          <t>61.976.100-6</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ACONCAGUA</t>
+          <t>SUPERINTENDENCIA DE CASINOS DE JUEGO</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -24729,12 +24725,12 @@
       </c>
       <c r="I377" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J377" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K377" t="inlineStr">
@@ -24748,13 +24744,13 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>16260.16</v>
+        <v>21128.69</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>688-100-CM26</t>
+          <t>1375746-102-CM26</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -24774,17 +24770,17 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>61.301.100-5</t>
+          <t>61.981.280-8</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>OFICINA DE ESTUDIOS Y POLITICAS AGRARIAS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ACONCAGUA</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -24794,12 +24790,12 @@
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K378" t="inlineStr">
@@ -24813,13 +24809,13 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>71574.92999999999</v>
+        <v>16260.16</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>514862-530-CM26</t>
+          <t>688-100-CM26</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -24834,22 +24830,22 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>71.234.100-9</t>
+          <t>61.301.100-5</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE PENALOLEN PARA EL DESARROLO SOCIAL CORMUP</t>
+          <t>OFICINA DE ESTUDIOS Y POLITICAS AGRARIAS</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -24859,17 +24855,17 @@
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K379" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L379" t="inlineStr">
@@ -24878,13 +24874,13 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>1901.77</v>
+        <v>71574.92999999999</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>1079713-481-CM26</t>
+          <t>514862-530-CM26</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -24899,22 +24895,22 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>53.322.604-3</t>
+          <t>71.234.100-9</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CORPORACION MUNICIPAL DE PENALOLEN PARA EL DESARROLO SOCIAL CORMUP</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -24943,13 +24939,13 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>1056.54</v>
+        <v>1901.77</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>1375757-515-CM26</t>
+          <t>1079713-481-CM26</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -24969,17 +24965,17 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>61.981.240-9</t>
+          <t>53.322.604-3</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PUELCHE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
@@ -24989,17 +24985,17 @@
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
@@ -25008,13 +25004,13 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>12580.68</v>
+        <v>1056.54</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>1260-126-SE26</t>
+          <t>1375757-515-CM26</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -25029,22 +25025,22 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>61.923.200-3</t>
+          <t>61.981.240-9</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PUELCHE</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -25054,17 +25050,17 @@
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>880443249</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K382" t="inlineStr">
         <is>
-          <t>Extranjero</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">
@@ -25073,13 +25069,13 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>106407.42</v>
+        <v>12580.68</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>188-517-CM26</t>
+          <t>1260-126-SE26</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -25099,17 +25095,17 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>70.933.700-9</t>
+          <t>61.923.200-3</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -25119,17 +25115,17 @@
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>880443249</t>
         </is>
       </c>
       <c r="K383" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Extranjero</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
@@ -25138,13 +25134,13 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>5810.39</v>
+        <v>106407.42</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>1147293-240-CM26</t>
+          <t>188-517-CM26</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -25169,12 +25165,12 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>70.930.000-8</t>
+          <t>70.933.700-9</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>Fundación para la Innovación Agraria</t>
+          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -25184,12 +25180,12 @@
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K384" t="inlineStr">
@@ -25203,13 +25199,13 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>17915.39</v>
+        <v>5810.39</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2412-522-CM26</t>
+          <t>1147293-240-CM26</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -25224,7 +25220,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -25234,12 +25230,12 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>69.254.100-6</t>
+          <t>70.930.000-8</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LO PRADO</t>
+          <t>Fundación para la Innovación Agraria</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -25249,12 +25245,12 @@
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K385" t="inlineStr">
@@ -25268,13 +25264,13 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>74764.49000000001</v>
+        <v>17915.39</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>858-348-SE26</t>
+          <t>2412-522-CM26</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -25289,7 +25285,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
@@ -25299,12 +25295,12 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.254.100-6</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE LO PRADO</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -25333,13 +25329,13 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>713286</v>
+        <v>74764.49000000001</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>867990-485-CM26</t>
+          <t>858-348-SE26</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -25359,17 +25355,17 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -25379,12 +25375,12 @@
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K387" t="inlineStr">
@@ -25398,13 +25394,13 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>224910</v>
+        <v>713286</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>2412-528-CM26</t>
+          <t>867990-485-CM26</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -25414,12 +25410,12 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
@@ -25429,12 +25425,12 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>69.254.100-6</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LO PRADO</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -25444,17 +25440,17 @@
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K388" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L388" t="inlineStr">
@@ -25463,13 +25459,13 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>10565.42</v>
+        <v>224910</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>604944-108-CM26</t>
+          <t>2412-528-CM26</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -25484,22 +25480,22 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>61.979.870-8</t>
+          <t>69.254.100-6</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DEFENSA</t>
+          <t>I MUNICIPALIDAD DE LO PRADO</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -25509,17 +25505,17 @@
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K389" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L389" t="inlineStr">
@@ -25528,13 +25524,13 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>8388.07</v>
+        <v>10565.42</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>587-431-CM26</t>
+          <t>604944-108-CM26</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -25549,7 +25545,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
@@ -25559,12 +25555,12 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>61.801.000-7</t>
+          <t>61.979.870-8</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>SUBSECRETARIA DE DEFENSA</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -25574,12 +25570,12 @@
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K390" t="inlineStr">
@@ -25593,13 +25589,13 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>13787.34</v>
+        <v>8388.07</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2733-421-CM26</t>
+          <t>587-431-CM26</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -25614,7 +25610,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -25624,12 +25620,12 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>69.071.700-K</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
@@ -25639,17 +25635,17 @@
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.334.381-2</t>
         </is>
       </c>
       <c r="K391" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L391" t="inlineStr">
@@ -25658,13 +25654,13 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>6339.25</v>
+        <v>13787.34</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>595636-75-CM26</t>
+          <t>2733-421-CM26</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -25679,7 +25675,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -25689,12 +25685,12 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>61.312.000-9</t>
+          <t>69.071.700-K</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>INIA</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
@@ -25704,17 +25700,17 @@
       </c>
       <c r="I392" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K392" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L392" t="inlineStr">
@@ -25723,13 +25719,13 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>62978.85</v>
+        <v>6339.25</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>2305-63-CM26</t>
+          <t>595636-75-CM26</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -25744,22 +25740,22 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>61.973.000-3</t>
+          <t>61.312.000-9</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>UNIDAD DE ANALISIS FINANCIERO</t>
+          <t>INIA</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
@@ -25769,12 +25765,12 @@
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K393" t="inlineStr">
@@ -25788,13 +25784,13 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>5158.29</v>
+        <v>62978.85</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>2981-1144-CM26</t>
+          <t>2305-63-CM26</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -25809,7 +25805,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -25819,12 +25815,12 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.973.000-3</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>UNIDAD DE ANALISIS FINANCIERO</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
@@ -25834,12 +25830,12 @@
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K394" t="inlineStr">
@@ -25853,13 +25849,13 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>5772.69</v>
+        <v>5158.29</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>979-1248-CM26</t>
+          <t>2981-1144-CM26</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -25879,17 +25875,17 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -25918,13 +25914,13 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>28709.51</v>
+        <v>5772.69</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>2434-37-CM26</t>
+          <t>979-1248-CM26</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -25949,12 +25945,12 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>69.254.300-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -25964,12 +25960,12 @@
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K396" t="inlineStr">
@@ -25983,13 +25979,13 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>120303.05</v>
+        <v>28709.51</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>619284-146-CM26</t>
+          <t>2434-37-CM26</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -26004,7 +26000,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -26014,12 +26010,12 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>61.980.000-1</t>
+          <t>69.254.300-9</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TRANSPORTES</t>
+          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
@@ -26029,12 +26025,12 @@
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K397" t="inlineStr">
@@ -26048,13 +26044,13 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>2751.09</v>
+        <v>120303.05</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>872-572-CM26</t>
+          <t>619284-146-CM26</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -26069,22 +26065,22 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>82.983.100-7</t>
+          <t>61.980.000-1</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>Comisión Chilena de Energía Nuclear</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -26094,12 +26090,12 @@
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>ORION 2000 SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>96.899.890-0</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K398" t="inlineStr">
@@ -26113,13 +26109,13 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>57068.83</v>
+        <v>2751.09</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>1533460-50-CM26</t>
+          <t>872-572-CM26</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -26134,22 +26130,22 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>65.261.347-0</t>
+          <t>82.983.100-7</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>CORPORACIÓN MUNICIPAL DE CULTURA, DEPORTE Y DE FOMENTO DE DESARROLLO C</t>
+          <t>Comisión Chilena de Energía Nuclear</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
@@ -26159,12 +26155,12 @@
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>ORION 2000 SPA</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>96.899.890-0</t>
         </is>
       </c>
       <c r="K399" t="inlineStr">
@@ -26178,13 +26174,13 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>3961.63</v>
+        <v>57068.83</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>3363-94-CM26</t>
+          <t>1533460-50-CM26</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -26204,17 +26200,17 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>61.101.045-1</t>
+          <t>65.261.347-0</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CORPORACIÓN MUNICIPAL DE CULTURA, DEPORTE Y DE FOMENTO DE DESARROLLO C</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
@@ -26224,12 +26220,12 @@
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K400" t="inlineStr">
@@ -26243,13 +26239,13 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>2498.75</v>
+        <v>3961.63</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2341-499-CM26</t>
+          <t>3363-94-CM26</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -26264,22 +26260,22 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>69.072.700-5</t>
+          <t>61.101.045-1</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
@@ -26289,28 +26285,32 @@
       </c>
       <c r="I401" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
-        </is>
-      </c>
-      <c r="K401" t="inlineStr"/>
+          <t>76.334.381-2</t>
+        </is>
+      </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>34986</v>
+        <v>2498.75</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>1385462-180-CM26</t>
+          <t>2341-499-CM26</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -26330,17 +26330,17 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>69.072.700-5</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
@@ -26350,32 +26350,28 @@
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K402" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.854.651-7</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr"/>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>6039.25</v>
+        <v>34986</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>188-596-CM26</t>
+          <t>1385462-180-CM26</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -26395,17 +26391,17 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>70.933.700-9</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
@@ -26415,12 +26411,12 @@
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K403" t="inlineStr">
@@ -26434,13 +26430,13 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>2235.26</v>
+        <v>6039.25</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>894778-42-CM26</t>
+          <t>188-596-CM26</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -26455,22 +26451,22 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>60.501.000-8</t>
+          <t>70.933.700-9</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL INTERIOR</t>
+          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
@@ -26480,12 +26476,12 @@
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K404" t="inlineStr">
@@ -26499,13 +26495,13 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>332367</v>
+        <v>2235.26</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>894778-43-SE26</t>
+          <t>894778-42-CM26</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -26520,7 +26516,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -26545,12 +26541,12 @@
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K405" t="inlineStr">
@@ -26564,13 +26560,13 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>30212.91</v>
+        <v>332367</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>1020-317-CM26</t>
+          <t>894778-43-SE26</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -26590,17 +26586,17 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.501.000-8</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SUBSECRETARIA DEL INTERIOR</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
@@ -26610,12 +26606,12 @@
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K406" t="inlineStr">
@@ -26629,13 +26625,13 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>39342.59</v>
+        <v>30212.91</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>812261-1397-CM26</t>
+          <t>1020-317-CM26</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -26660,12 +26656,12 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
@@ -26675,28 +26671,32 @@
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K407" t="inlineStr"/>
+          <t>76.083.145-k</t>
+        </is>
+      </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L407" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>223910.4</v>
+        <v>39342.59</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>598-250-SE26</t>
+          <t>812261-1397-CM26</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -26711,22 +26711,22 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>61.513.000-1</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>DIRECCION PREVISION DE CARABINEROS DE CHILE</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -26736,32 +26736,28 @@
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>Seidor Chile S.A.</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>96.986.170-4</t>
-        </is>
-      </c>
-      <c r="K408" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr"/>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>340177.13</v>
+        <v>223910.4</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>743848-35-CM26</t>
+          <t>598-250-SE26</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -26771,27 +26767,27 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>oct-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>61.980.250-0</t>
+          <t>61.513.000-1</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>SEGUNDO TRIBUNAL AMBIENTAL</t>
+          <t>DIRECCION PREVISION DE CARABINEROS DE CHILE</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
@@ -26801,12 +26797,12 @@
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>Seidor Chile S.A.</t>
         </is>
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>96.986.170-4</t>
         </is>
       </c>
       <c r="K409" t="inlineStr">
@@ -26820,13 +26816,13 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>19038.1</v>
+        <v>340177.13</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>857-148-CM26</t>
+          <t>743848-35-CM26</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -26851,12 +26847,12 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>72.576.700-5</t>
+          <t>61.980.250-0</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE LA DISCAPACIDAD</t>
+          <t>SEGUNDO TRIBUNAL AMBIENTAL</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -26866,12 +26862,12 @@
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K410" t="inlineStr">
@@ -26885,13 +26881,13 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>19335.95</v>
+        <v>19038.1</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>2287-784-CM26</t>
+          <t>857-148-CM26</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -26906,7 +26902,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
@@ -26916,12 +26912,12 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>69.253.700-9</t>
+          <t>72.576.700-5</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MACUL</t>
+          <t>SERVICIO NACIONAL DE LA DISCAPACIDAD</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
@@ -26950,13 +26946,13 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>23436.34</v>
+        <v>19335.95</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>1301883-261-CM26</t>
+          <t>2287-784-CM26</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -26971,7 +26967,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -26981,12 +26977,12 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.253.700-9</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MACUL</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -26996,12 +26992,12 @@
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K412" t="inlineStr">
@@ -27015,13 +27011,13 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>2751.09</v>
+        <v>23436.34</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>1029940-84-CM26</t>
+          <t>1301883-261-CM26</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -27046,12 +27042,12 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>62.000.370-0</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL PATRIMONIO CULTURAL</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
@@ -27061,12 +27057,12 @@
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J413" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K413" t="inlineStr">
@@ -27080,13 +27076,13 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>12772.39</v>
+        <v>2751.09</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>1561-180-CM26</t>
+          <t>1029940-84-CM26</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -27111,12 +27107,12 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>61.504.000-2</t>
+          <t>62.000.370-0</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DEL CREDITO PRENDARIO</t>
+          <t>SUBSECRETARIA DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -27126,12 +27122,12 @@
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K414" t="inlineStr">
@@ -27145,13 +27141,13 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>8597.16</v>
+        <v>12772.39</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>539119-3323-CM26</t>
+          <t>1561-180-CM26</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -27166,7 +27162,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -27176,12 +27172,12 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>61.504.000-2</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION GENERAL DEL CREDITO PRENDARIO</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
@@ -27191,12 +27187,12 @@
       </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J415" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K415" t="inlineStr">
@@ -27210,13 +27206,13 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>1171.82</v>
+        <v>8597.16</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>628-114-CM26</t>
+          <t>539119-3323-CM26</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -27231,7 +27227,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
@@ -27241,12 +27237,12 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>60.107.000-6</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
@@ -27256,12 +27252,12 @@
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J416" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K416" t="inlineStr">
@@ -27275,13 +27271,13 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>94562.16</v>
+        <v>1171.82</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>1020-334-CM26</t>
+          <t>628-114-CM26</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -27296,7 +27292,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -27306,12 +27302,12 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.107.000-6</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
@@ -27340,13 +27336,13 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>1692.41</v>
+        <v>94562.16</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>2153-631-CM26</t>
+          <t>1020-334-CM26</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -27371,12 +27367,12 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>61.608.503-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>Hospital Sanatorio San José de Maipo</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
@@ -27386,12 +27382,12 @@
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J418" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K418" t="inlineStr">
@@ -27405,13 +27401,13 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>15655.64</v>
+        <v>1692.41</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>1230771-41-CM26</t>
+          <t>2153-631-CM26</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -27426,7 +27422,7 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
@@ -27436,12 +27432,12 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>65.080.277-2</t>
+          <t>61.608.503-4</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>Corporación de Desarrollo Social de la Municipalidad de Independencia</t>
+          <t>Hospital Sanatorio San José de Maipo</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
@@ -27451,12 +27447,12 @@
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K419" t="inlineStr">
@@ -27470,13 +27466,13 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>1774.05</v>
+        <v>15655.64</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>4931-123-CM26</t>
+          <t>1230771-41-CM26</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -27491,7 +27487,7 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -27501,12 +27497,12 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>65.613.130-6</t>
+          <t>65.080.277-2</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>COMISION ADMINISTRADORA DEL SISTEMA DE CREDITOS P. ESTUDIOS SUPERIORES</t>
+          <t>Corporación de Desarrollo Social de la Municipalidad de Independencia</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
@@ -27516,12 +27512,12 @@
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K420" t="inlineStr">
@@ -27535,71 +27531,136 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>1719.43</v>
+        <v>1774.05</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
+          <t>4931-123-CM26</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>65.613.130-6</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>COMISION ADMINISTRADORA DEL SISTEMA DE CREDITOS P. ESTUDIOS SUPERIORES</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>Intercity S.A.</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M421" s="2" t="n">
+        <v>1719.43</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
           <t>2982-90-CM26</t>
         </is>
       </c>
-      <c r="B421" t="inlineStr">
-        <is>
-          <t>2239-11-LR24</t>
-        </is>
-      </c>
-      <c r="C421" t="inlineStr">
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
         <is>
           <t>oct-2026</t>
         </is>
       </c>
-      <c r="D421" t="inlineStr">
+      <c r="D422" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E421" t="inlineStr">
+      <c r="E422" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F421" t="inlineStr">
+      <c r="F422" t="inlineStr">
         <is>
           <t>60.506.000-5</t>
         </is>
       </c>
-      <c r="G421" t="inlineStr">
+      <c r="G422" t="inlineStr">
         <is>
           <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
-      <c r="H421" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I421" t="inlineStr">
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
         <is>
           <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
-      <c r="J421" t="inlineStr">
+      <c r="J422" t="inlineStr">
         <is>
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L421" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M421" s="2" t="n">
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M422" s="2" t="n">
         <v>7481.38</v>
       </c>
     </row>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/metropolitana.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/metropolitana.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M422"/>
+  <dimension ref="A1:M424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8311,7 +8311,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>797305-87-CM25</t>
+          <t>618923-218-CM25</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>61.005.000-k</t>
+          <t>61.979.970-4</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE INSOLVENCIA Y REEMPRENDIMIENTO</t>
+          <t>SUBSECRETARIA PARA LAS FUERZAS ARMADAS</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8351,26 +8351,22 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>75963.64999999999</v>
+        <v>185452.93</v>
       </c>
     </row>
     <row r="124">
@@ -8441,7 +8437,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>618923-218-CM25</t>
+          <t>797305-87-CM25</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8466,12 +8462,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>61.979.970-4</t>
+          <t>61.005.000-k</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA PARA LAS FUERZAS ARMADAS</t>
+          <t>SUPERINTENDENCIA DE INSOLVENCIA Y REEMPRENDIMIENTO</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8481,28 +8477,32 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>185452.93</v>
+        <v>75963.64999999999</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>3181-407-SE25</t>
+          <t>1121-93-SE25</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>69.080.200-7</t>
+          <t>61.706.000-0</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MACHALI</t>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -8561,13 +8561,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>244188</v>
+        <v>30696.59</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1121-93-SE25</t>
+          <t>3181-407-SE25</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8592,12 +8592,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>61.706.000-0</t>
+          <t>69.080.200-7</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Comisión Chilena del Cobre - COCHILCO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MACHALI</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8607,12 +8607,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -8626,7 +8626,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>30696.59</v>
+        <v>244188</v>
       </c>
     </row>
     <row r="128">
@@ -8758,7 +8758,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1375746-55-CM25</t>
+          <t>1271178-319-CM25</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>61.981.280-8</t>
+          <t>71.369.900-4</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ACONCAGUA</t>
+          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL DE MACUL</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8798,12 +8798,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.334.381-2</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -8817,13 +8817,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>13907.53</v>
+        <v>1281.63</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1271178-319-CM25</t>
+          <t>1375746-55-CM25</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8848,12 +8848,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>71.369.900-4</t>
+          <t>61.981.280-8</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL DE MACUL</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ACONCAGUA</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8863,12 +8863,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -8882,7 +8882,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>1281.63</v>
+        <v>13907.53</v>
       </c>
     </row>
     <row r="132">
@@ -9530,7 +9530,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>587-657-CM25</t>
+          <t>519302-150-CM25</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>61.801.000-7</t>
+          <t>65.999.669-3</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>INSTITUTO NACIONAL DE PROPIEDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9589,7 +9589,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>14172.9</v>
+        <v>10150.22</v>
       </c>
     </row>
     <row r="143">
@@ -9660,7 +9660,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>519302-150-CM25</t>
+          <t>587-657-CM25</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>65.999.669-3</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE PROPIEDAD INDUSTRIAL</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9719,13 +9719,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>10150.22</v>
+        <v>14172.9</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>623663-460-CM25</t>
+          <t>628-339-CM25</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9745,17 +9745,17 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>65.030.848-4</t>
+          <t>60.107.000-6</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>AGENCIA CHILENA DE EFICIENCIA ENERGETICA</t>
+          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -9784,13 +9784,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>36945.22</v>
+        <v>82419.39999999999</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>628-339-CM25</t>
+          <t>623663-460-CM25</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9810,17 +9810,17 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>60.107.000-6</t>
+          <t>65.030.848-4</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
+          <t>AGENCIA CHILENA DE EFICIENCIA ENERGETICA</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -9849,7 +9849,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>82419.39999999999</v>
+        <v>36945.22</v>
       </c>
     </row>
     <row r="147">
@@ -10237,7 +10237,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1019-549-CM25</t>
+          <t>608897-11250-CM25</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -10262,12 +10262,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.979.930-5</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -10277,28 +10277,32 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>73666.52</v>
+        <v>9727.92</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1019-548-CM25</t>
+          <t>1019-549-CM25</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -10338,32 +10342,28 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>4863.77</v>
+        <v>73666.52</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>608897-11250-CM25</t>
+          <t>1019-548-CM25</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>61.979.930-5</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -10422,7 +10422,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>9727.92</v>
+        <v>4863.77</v>
       </c>
     </row>
     <row r="156">
@@ -12748,7 +12748,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>937232-1136-CM25</t>
+          <t>1260-276-CM25</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12773,12 +12773,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>61.980.620-4</t>
+          <t>61.923.200-3</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>CENTRO DE REFERENCIA DE SALUD HOSPITAL PROVINCIA CORDILLERA</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.334.381-2</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -12807,13 +12807,13 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>92320.2</v>
+        <v>19852.06</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1260-276-CM25</t>
+          <t>937232-1136-CM25</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12838,12 +12838,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>61.923.200-3</t>
+          <t>61.980.620-4</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>CENTRO DE REFERENCIA DE SALUD HOSPITAL PROVINCIA CORDILLERA</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12853,12 +12853,12 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -12872,7 +12872,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>19852.06</v>
+        <v>92320.2</v>
       </c>
     </row>
     <row r="194">
@@ -13203,7 +13203,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1121-150-CM25</t>
+          <t>1057468-288-CM25</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -13228,12 +13228,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>61.706.000-0</t>
+          <t>61.608.600-6</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Comisión Chilena del Cobre - COCHILCO</t>
+          <t>SERVICIO DE SALUD METROPOLITANO CENTRAL</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -13243,12 +13243,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -13262,13 +13262,13 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>3611.55</v>
+        <v>13321.42</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1057468-288-CM25</t>
+          <t>1121-150-CM25</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -13293,12 +13293,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>61.608.600-6</t>
+          <t>61.706.000-0</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO CENTRAL</t>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -13308,12 +13308,12 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -13327,7 +13327,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>13321.42</v>
+        <v>3611.55</v>
       </c>
     </row>
     <row r="201">
@@ -14499,7 +14499,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1385462-330-CM25</t>
+          <t>1057491-21303-CM25</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -14519,17 +14519,17 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>61.608.408-9</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -14539,12 +14539,12 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>SEIDOR TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.449.580-2</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
@@ -14558,13 +14558,13 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>22983.66</v>
+        <v>99960</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1057491-21303-CM25</t>
+          <t>1068038-145-CM25</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -14584,17 +14584,17 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>61.608.408-9</t>
+          <t>60.511.000-2</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
+          <t>SUBSECRETARIA DEL INTERIOR</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -14604,12 +14604,12 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>SEIDOR TECHNOLOGIES S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>76.449.580-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -14623,13 +14623,13 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>99960</v>
+        <v>3804.83</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1068038-145-CM25</t>
+          <t>1385462-330-CM25</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -14654,12 +14654,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>60.511.000-2</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL INTERIOR</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -14669,12 +14669,12 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -14688,7 +14688,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>3804.83</v>
+        <v>22983.66</v>
       </c>
     </row>
     <row r="222">
@@ -15925,7 +15925,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>1238177-14-CM26</t>
+          <t>539119-470-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15950,12 +15950,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>65.165.009-7</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SEGURIDAD CIUDADANA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -15965,12 +15965,12 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
@@ -15984,13 +15984,13 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>3534.3</v>
+        <v>1056.9</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>539119-470-CM26</t>
+          <t>1238177-14-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -16015,12 +16015,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>65.165.009-7</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SEGURIDAD CIUDADANA</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -16030,12 +16030,12 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
@@ -16049,7 +16049,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>1056.9</v>
+        <v>3534.3</v>
       </c>
     </row>
     <row r="243">
@@ -16376,7 +16376,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1415862-13-CM26</t>
+          <t>1372962-3-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -16396,17 +16396,17 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>61.533.000-0</t>
+          <t>65.143.474-2</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
+          <t>FUNDACION PARA LA REHABILITACIÓN DE PERSONAS CON DISCAPACIDAD DE LA COMUNA DE SAN PEDRO DE ATACAMA</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -16435,13 +16435,13 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>70962.08</v>
+        <v>1651.17</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>1372962-3-CM26</t>
+          <t>1415862-13-CM26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -16461,17 +16461,17 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>65.143.474-2</t>
+          <t>61.533.000-0</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>FUNDACION PARA LA REHABILITACIÓN DE PERSONAS CON DISCAPACIDAD DE LA COMUNA DE SAN PEDRO DE ATACAMA</t>
+          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -16500,7 +16500,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>1651.17</v>
+        <v>70962.08</v>
       </c>
     </row>
     <row r="250">
@@ -17534,7 +17534,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>1592-29-CM26</t>
+          <t>1592-28-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -17574,12 +17574,12 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.334.381-2</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
@@ -17593,13 +17593,13 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>12272.14</v>
+        <v>16439.18</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>1592-28-CM26</t>
+          <t>1592-29-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -17639,12 +17639,12 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
@@ -17658,7 +17658,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>16439.18</v>
+        <v>12272.14</v>
       </c>
     </row>
     <row r="268">
@@ -18497,7 +18497,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2343-162-CM26</t>
+          <t>1428670-72-CM26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -18517,17 +18517,17 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>69.070.100-6</t>
+          <t>65.117.794-4</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTIAGO</t>
+          <t>ASOCIACION METROPOLITANA DE MUNICIPALIDADES DE SANTIAGO SUR PARA LA GE</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -18537,32 +18537,28 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K281" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>79.770.640-k</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>2536.13</v>
+        <v>9507.48</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>1428670-72-CM26</t>
+          <t>699360-19-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -18582,17 +18578,17 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>65.117.794-4</t>
+          <t>60.505.000-k</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>ASOCIACION METROPOLITANA DE MUNICIPALIDADES DE SANTIAGO SUR PARA LA GE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -18602,28 +18598,32 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>79.770.640-k</t>
-        </is>
-      </c>
-      <c r="K282" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>9507.48</v>
+        <v>4325.59</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>699360-19-CM26</t>
+          <t>2343-162-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -18648,12 +18648,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>60.505.000-k</t>
+          <t>69.070.100-6</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE SANTIAGO</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -18663,17 +18663,17 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
@@ -18682,7 +18682,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>4325.59</v>
+        <v>2536.13</v>
       </c>
     </row>
     <row r="284">
@@ -18883,7 +18883,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>1351461-18-CM26</t>
+          <t>1238177-77-CM26</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -18908,12 +18908,12 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>60.801.000-9</t>
+          <t>65.165.009-7</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SEGURIDAD CIUDADANA</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -18923,12 +18923,12 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
@@ -18942,13 +18942,13 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>26155.37</v>
+        <v>1031.66</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>1238177-77-CM26</t>
+          <t>1020-136-CM26</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -18968,17 +18968,17 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>65.165.009-7</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SEGURIDAD CIUDADANA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -19007,13 +19007,13 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>1031.66</v>
+        <v>2579.15</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>1020-136-CM26</t>
+          <t>1351461-18-CM26</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -19033,17 +19033,17 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.801.000-9</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -19053,12 +19053,12 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
@@ -19072,7 +19072,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>2579.15</v>
+        <v>26155.37</v>
       </c>
     </row>
     <row r="290">
@@ -19269,7 +19269,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>577290-48-CM26</t>
+          <t>2069-4322-CM26</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -19294,12 +19294,12 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>61.979.750-7</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TRANSPORTES</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -19309,12 +19309,12 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
@@ -19328,13 +19328,13 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>4226.88</v>
+        <v>1031.66</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2069-4322-CM26</t>
+          <t>577290-48-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -19359,12 +19359,12 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.979.750-7</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -19374,12 +19374,12 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
@@ -19393,7 +19393,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>1031.66</v>
+        <v>4226.88</v>
       </c>
     </row>
     <row r="295">
@@ -19529,7 +19529,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>577290-45-CM26</t>
+          <t>14-185-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>61.979.750-7</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TRANSPORTES</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -19569,28 +19569,32 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>79.770.640-k</t>
-        </is>
-      </c>
-      <c r="K297" t="inlineStr"/>
+          <t>76.083.145-k</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>2579.33</v>
+        <v>3846.89</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>14-186-CM26</t>
+          <t>577290-45-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -19615,12 +19619,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>61.979.750-7</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -19630,32 +19634,28 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
-        </is>
-      </c>
-      <c r="K298" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.770.640-k</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr"/>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>17602.43</v>
+        <v>2579.33</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>14-187-CM26</t>
+          <t>14-189-CM26</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -19714,13 +19714,13 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>17485.86</v>
+        <v>3497.17</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>14-188-CM26</t>
+          <t>14-186-CM26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -19779,13 +19779,13 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>13638.97</v>
+        <v>17602.43</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>14-185-CM26</t>
+          <t>14-190-CM26</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -19844,13 +19844,13 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>3846.89</v>
+        <v>2797.74</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>14-190-CM26</t>
+          <t>14-188-CM26</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -19909,13 +19909,13 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>2797.74</v>
+        <v>13638.97</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>14-189-CM26</t>
+          <t>14-187-CM26</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -19974,7 +19974,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>3497.17</v>
+        <v>17485.86</v>
       </c>
     </row>
     <row r="304">
@@ -20045,7 +20045,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>577290-47-CM26</t>
+          <t>188-371-CM26</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -20065,17 +20065,17 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>61.979.750-7</t>
+          <t>70.933.700-9</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TRANSPORTES</t>
+          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -20085,32 +20085,28 @@
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
-        </is>
-      </c>
-      <c r="K305" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.770.640-k</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr"/>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>999.6</v>
+        <v>17002.6</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>188-371-CM26</t>
+          <t>577290-47-CM26</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -20130,17 +20126,17 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>70.933.700-9</t>
+          <t>61.979.750-7</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -20150,22 +20146,26 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>79.770.640-k</t>
-        </is>
-      </c>
-      <c r="K306" t="inlineStr"/>
+          <t>76.288.338-4</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>17002.6</v>
+        <v>999.6</v>
       </c>
     </row>
     <row r="307">
@@ -20549,7 +20549,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2793-487-CM26</t>
+          <t>2341-226-CM26</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -20574,12 +20574,12 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>69.072.700-5</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Municipalidad de Huechuraba</t>
+          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -20589,12 +20589,12 @@
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.334.381-2</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
@@ -20608,13 +20608,13 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>402884.5</v>
+        <v>39217.54</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2341-226-CM26</t>
+          <t>705290-1047-CM26</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -20634,17 +20634,17 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>69.072.700-5</t>
+          <t>61.608.205-1</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
+          <t>SERVICIO SALUD OCCIDENTE HOSPITAL DR FELIX BULNES CERDA</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -20654,12 +20654,12 @@
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K314" t="inlineStr">
@@ -20673,13 +20673,13 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>39217.54</v>
+        <v>44351.3</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>705290-1047-CM26</t>
+          <t>2793-487-CM26</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -20699,17 +20699,17 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>61.608.205-1</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD OCCIDENTE HOSPITAL DR FELIX BULNES CERDA</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -20738,7 +20738,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>44351.3</v>
+        <v>402884.5</v>
       </c>
     </row>
     <row r="316">
@@ -20935,7 +20935,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>4928-25-CM26</t>
+          <t>1388961-384-CM26</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -20960,12 +20960,12 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>65.118.035-K</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>ASOCIACION DE MUNICIPALIDADES PARA LA SEGURIDAD CIUDADANA EN LA ZONA ORIENTE</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -20975,12 +20975,12 @@
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
@@ -20994,13 +20994,13 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>1690.75</v>
+        <v>44627.86</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>1388961-384-CM26</t>
+          <t>4928-25-CM26</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -21025,12 +21025,12 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>65.118.035-K</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>ASOCIACION DE MUNICIPALIDADES PARA LA SEGURIDAD CIUDADANA EN LA ZONA ORIENTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -21040,12 +21040,12 @@
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
@@ -21059,7 +21059,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>44627.86</v>
+        <v>1690.75</v>
       </c>
     </row>
     <row r="321">
@@ -21451,7 +21451,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>1315526-15-CM26</t>
+          <t>1368-34-CM26</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -21476,12 +21476,12 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>65.086.019-5</t>
+          <t>75.980.060-5</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Centro Ideactiva</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -21510,13 +21510,13 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>7692.76</v>
+        <v>10769.86</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>1368-34-CM26</t>
+          <t>5768-102-CM26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -21536,17 +21536,17 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>75.980.060-5</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -21556,12 +21556,12 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
@@ -21575,7 +21575,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>10769.86</v>
+        <v>54978</v>
       </c>
     </row>
     <row r="329">
@@ -21772,7 +21772,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>5768-102-CM26</t>
+          <t>1315526-15-CM26</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -21792,17 +21792,17 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>65.086.019-5</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>Centro Ideactiva</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -21812,12 +21812,12 @@
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
@@ -21831,7 +21831,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>54978</v>
+        <v>7692.76</v>
       </c>
     </row>
     <row r="333">
@@ -22227,7 +22227,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>539119-2289-CM26</t>
+          <t>1561-110-CM26</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -22247,17 +22247,17 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>61.504.000-2</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION GENERAL DEL CREDITO PRENDARIO</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -22267,32 +22267,28 @@
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K339" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr"/>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>845.23</v>
+        <v>11195.52</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>1561-110-CM26</t>
+          <t>539119-2289-CM26</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -22312,17 +22308,17 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>61.504.000-2</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DEL CREDITO PRENDARIO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -22332,22 +22328,26 @@
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K340" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>11195.52</v>
+        <v>845.23</v>
       </c>
     </row>
     <row r="341">
@@ -22418,7 +22418,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>858-254-CM26</t>
+          <t>1561-109-CM26</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -22443,12 +22443,12 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.504.000-2</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>DIRECCION GENERAL DEL CREDITO PRENDARIO</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -22458,32 +22458,28 @@
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
-        </is>
-      </c>
-      <c r="K342" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr"/>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>4470.52</v>
+        <v>142889.96</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>1561-109-CM26</t>
+          <t>858-254-CM26</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -22508,12 +22504,12 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>61.504.000-2</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DEL CREDITO PRENDARIO</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -22523,22 +22519,26 @@
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K343" t="inlineStr"/>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>142889.96</v>
+        <v>4470.52</v>
       </c>
     </row>
     <row r="344">
@@ -22674,7 +22674,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>1533460-23-CM26</t>
+          <t>836578-87-CM26</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -22699,12 +22699,12 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>65.261.347-0</t>
+          <t>61.101.045-1</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>CORPORACIÓN MUNICIPAL DE CULTURA, DEPORTE Y DE FOMENTO DE DESARROLLO C</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -22714,12 +22714,12 @@
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.334.381-2</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
@@ -22733,13 +22733,13 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>7130.93</v>
+        <v>1308.87</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>836578-87-CM26</t>
+          <t>1533460-23-CM26</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -22764,12 +22764,12 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>61.101.045-1</t>
+          <t>65.261.347-0</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CORPORACIÓN MUNICIPAL DE CULTURA, DEPORTE Y DE FOMENTO DE DESARROLLO C</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -22779,12 +22779,12 @@
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K347" t="inlineStr">
@@ -22798,7 +22798,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>1308.87</v>
+        <v>7130.93</v>
       </c>
     </row>
     <row r="348">
@@ -23259,7 +23259,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>585-94-CM26</t>
+          <t>514862-462-CM26</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -23284,12 +23284,12 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>71.234.100-9</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>CORPORACION MUNICIPAL DE PENALOLEN PARA EL DESARROLO SOCIAL CORMUP</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -23299,12 +23299,12 @@
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K355" t="inlineStr">
@@ -23318,13 +23318,13 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>326243.38</v>
+        <v>21360.5</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>514862-462-CM26</t>
+          <t>585-94-CM26</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -23349,12 +23349,12 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>71.234.100-9</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE PENALOLEN PARA EL DESARROLO SOCIAL CORMUP</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -23364,12 +23364,12 @@
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K356" t="inlineStr">
@@ -23383,7 +23383,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>21360.5</v>
+        <v>326243.38</v>
       </c>
     </row>
     <row r="357">
@@ -23454,7 +23454,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>1606-281-CM26</t>
+          <t>1750-263-CM26</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -23479,12 +23479,12 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>60.108.000-1</t>
+          <t>65.290.590-0</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>AGENCIA CHILENA DE COOPERACION INTERNACIONAL PARA EL DESARROLLO</t>
+          <t>DIRECCION NACIONAL DEL SERVICIO CIVIL</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -23494,12 +23494,12 @@
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K358" t="inlineStr">
@@ -23513,13 +23513,13 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>6082.09</v>
+        <v>10644.31</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>1750-263-CM26</t>
+          <t>2732-21-CM26</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -23539,17 +23539,17 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>65.290.590-0</t>
+          <t>69.071.700-K</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>DIRECCION NACIONAL DEL SERVICIO CIVIL</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -23578,13 +23578,13 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>10644.31</v>
+        <v>165430.94</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2732-21-CM26</t>
+          <t>1606-281-CM26</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -23604,17 +23604,17 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>69.071.700-K</t>
+          <t>60.108.000-1</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
+          <t>AGENCIA CHILENA DE COOPERACION INTERNACIONAL PARA EL DESARROLLO</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -23624,12 +23624,12 @@
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K360" t="inlineStr">
@@ -23643,7 +23643,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>165430.94</v>
+        <v>6082.09</v>
       </c>
     </row>
     <row r="361">
@@ -23844,7 +23844,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>595636-60-CM26</t>
+          <t>604944-82-CM26</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -23864,17 +23864,17 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>61.312.000-9</t>
+          <t>61.979.870-8</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>INIA</t>
+          <t>SUBSECRETARIA DE DEFENSA</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -23884,17 +23884,17 @@
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K364" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L364" t="inlineStr">
@@ -23903,13 +23903,13 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>845.23</v>
+        <v>11132.26</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>3894-65-CM26</t>
+          <t>595636-60-CM26</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -23934,12 +23934,12 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>69.071.400-0</t>
+          <t>61.312.000-9</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAMPA</t>
+          <t>INIA</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -23949,17 +23949,17 @@
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K365" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
@@ -23968,13 +23968,13 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>64867.5</v>
+        <v>845.23</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>604944-82-CM26</t>
+          <t>3894-65-CM26</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -23994,17 +23994,17 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>61.979.870-8</t>
+          <t>69.071.400-0</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DEFENSA</t>
+          <t>I MUNICIPALIDAD DE LAMPA</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -24014,12 +24014,12 @@
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K366" t="inlineStr">
@@ -24033,13 +24033,13 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>11132.26</v>
+        <v>64867.5</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>1271178-266-CM26</t>
+          <t>1237849-145-CM26</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -24064,12 +24064,12 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>71.369.900-4</t>
+          <t>65.081.056-2</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL DE MACUL</t>
+          <t>CORPORACION MUNICIPAL DE FOMENTO AL DESARROLLO COMUNAL Y PRODUCTIVO DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -24079,17 +24079,17 @@
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K367" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
@@ -24098,13 +24098,13 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>1479.16</v>
+        <v>3077.1</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>1237849-145-CM26</t>
+          <t>188-507-CM26</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -24124,17 +24124,17 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>65.081.056-2</t>
+          <t>70.933.700-9</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE FOMENTO AL DESARROLLO COMUNAL Y PRODUCTIVO DE LA FLORIDA</t>
+          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
@@ -24144,32 +24144,28 @@
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K368" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.854.651-7</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr"/>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>3077.1</v>
+        <v>34153</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>188-507-CM26</t>
+          <t>1271178-266-CM26</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -24189,17 +24185,17 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>70.933.700-9</t>
+          <t>71.369.900-4</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
+          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL DE MACUL</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -24209,22 +24205,26 @@
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
-        </is>
-      </c>
-      <c r="K369" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>34153</v>
+        <v>1479.16</v>
       </c>
     </row>
     <row r="370">
@@ -24360,7 +24360,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>1121-83-CM26</t>
+          <t>1121-84-CM26</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -24400,12 +24400,12 @@
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K372" t="inlineStr">
@@ -24419,13 +24419,13 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>30913.52</v>
+        <v>7909.38</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>1121-84-CM26</t>
+          <t>1393575-77-CM26</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -24450,12 +24450,12 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>61.706.000-0</t>
+          <t>65.010.882-5</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>Comisión Chilena del Cobre - COCHILCO</t>
+          <t>FUNDACION IMAGEN DE CHILE</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -24465,12 +24465,12 @@
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K373" t="inlineStr">
@@ -24484,13 +24484,13 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>7909.38</v>
+        <v>1422.05</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>1393575-77-CM26</t>
+          <t>1287766-76-CM26</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -24510,17 +24510,17 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>65.010.882-5</t>
+          <t>65.199.980-4</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>FUNDACION IMAGEN DE CHILE</t>
+          <t>Corporación Municipal de Deportes de Ñuñoa</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -24530,12 +24530,12 @@
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K374" t="inlineStr">
@@ -24549,13 +24549,13 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>1422.05</v>
+        <v>4080.32</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>1287766-76-CM26</t>
+          <t>1121-83-CM26</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -24575,17 +24575,17 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>65.199.980-4</t>
+          <t>61.706.000-0</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Deportes de Ñuñoa</t>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -24595,12 +24595,12 @@
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K375" t="inlineStr">
@@ -24614,7 +24614,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>4080.32</v>
+        <v>30913.52</v>
       </c>
     </row>
     <row r="376">
@@ -24945,7 +24945,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>1079713-481-CM26</t>
+          <t>1375757-515-CM26</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -24965,17 +24965,17 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>53.322.604-3</t>
+          <t>61.981.240-9</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PUELCHE</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
@@ -24985,17 +24985,17 @@
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
@@ -25004,13 +25004,13 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>1056.54</v>
+        <v>12580.68</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>1375757-515-CM26</t>
+          <t>1079713-481-CM26</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -25030,17 +25030,17 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>61.981.240-9</t>
+          <t>53.322.604-3</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PUELCHE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -25050,17 +25050,17 @@
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K382" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">
@@ -25069,7 +25069,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>12580.68</v>
+        <v>1056.54</v>
       </c>
     </row>
     <row r="383">
@@ -25140,7 +25140,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>188-517-CM26</t>
+          <t>1147293-240-CM26</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -25165,12 +25165,12 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>70.933.700-9</t>
+          <t>70.930.000-8</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
+          <t>Fundación para la Innovación Agraria</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -25180,12 +25180,12 @@
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K384" t="inlineStr">
@@ -25199,13 +25199,13 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>5810.39</v>
+        <v>17915.39</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>1147293-240-CM26</t>
+          <t>188-517-CM26</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -25230,12 +25230,12 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>70.930.000-8</t>
+          <t>70.933.700-9</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>Fundación para la Innovación Agraria</t>
+          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -25245,12 +25245,12 @@
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K385" t="inlineStr">
@@ -25264,7 +25264,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>17915.39</v>
+        <v>5810.39</v>
       </c>
     </row>
     <row r="386">
@@ -26200,7 +26200,7 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
@@ -27472,7 +27472,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>1230771-41-CM26</t>
+          <t>623663-205-CM26</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -27487,7 +27487,7 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -27497,12 +27497,12 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>65.080.277-2</t>
+          <t>65.030.848-4</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>Corporación de Desarrollo Social de la Municipalidad de Independencia</t>
+          <t>AGENCIA CHILENA DE EFICIENCIA ENERGETICA</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
@@ -27531,13 +27531,13 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>1774.05</v>
+        <v>19693.45</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>4931-123-CM26</t>
+          <t>1230771-41-CM26</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -27552,7 +27552,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
@@ -27562,12 +27562,12 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>65.613.130-6</t>
+          <t>65.080.277-2</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>COMISION ADMINISTRADORA DEL SISTEMA DE CREDITOS P. ESTUDIOS SUPERIORES</t>
+          <t>Corporación de Desarrollo Social de la Municipalidad de Independencia</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
@@ -27577,12 +27577,12 @@
       </c>
       <c r="I421" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J421" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K421" t="inlineStr">
@@ -27596,7 +27596,7 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>1719.43</v>
+        <v>1774.05</v>
       </c>
     </row>
     <row r="422">
@@ -27662,6 +27662,136 @@
       </c>
       <c r="M422" s="2" t="n">
         <v>7481.38</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>4931-123-CM26</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>65.613.130-6</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>COMISION ADMINISTRADORA DEL SISTEMA DE CREDITOS P. ESTUDIOS SUPERIORES</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>Intercity S.A.</t>
+        </is>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M423" s="2" t="n">
+        <v>1719.43</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>717503-304-CM26</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>69.265.990-2</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>Asociación Chilena de Municipalidades</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M424" s="2" t="n">
+        <v>8255.860000000001</v>
       </c>
     </row>
   </sheetData>
